--- a/database/event/1977/event_1977_evp_summary.xlsx
+++ b/database/event/1977/event_1977_evp_summary.xlsx
@@ -492,81 +492,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.898</v>
+        <v>4.9375</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7547</v>
+        <v>1.7689</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5573</v>
+        <v>1.5232</v>
       </c>
       <c r="E2" t="n">
-        <v>4.898</v>
+        <v>4.9375</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0775</v>
+        <v>2.225</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8204</v>
+        <v>2.7125</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0775</v>
+        <v>2.225</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6839</v>
+        <v>1.8034</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8204</v>
+        <v>2.7125</v>
       </c>
       <c r="K2" t="n">
-        <v>144</v>
+        <v>44</v>
       </c>
       <c r="L2" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M2" t="n">
-        <v>4.5043</v>
+        <v>4.5159</v>
       </c>
       <c r="N2" t="n">
-        <v>266</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.8048</v>
+        <v>4.898</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7213</v>
+        <v>1.7547</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5197</v>
+        <v>1.5075</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8048</v>
+        <v>4.898</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2525</v>
+        <v>2.0775</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5523</v>
+        <v>2.8204</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5485</v>
+        <v>2.0775</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6866</v>
+        <v>1.6839</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5523</v>
+        <v>2.8204</v>
       </c>
       <c r="K3" t="n">
         <v>144</v>
@@ -575,7 +575,7 @@
         <v>122</v>
       </c>
       <c r="M3" t="n">
-        <v>4.2389</v>
+        <v>4.5043</v>
       </c>
       <c r="N3" t="n">
         <v>266</v>
@@ -584,139 +584,139 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.5196</v>
+        <v>4.8048</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6192</v>
+        <v>1.7213</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4045</v>
+        <v>1.4703</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5196</v>
+        <v>4.8048</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8071</v>
+        <v>4.2525</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7125</v>
+        <v>0.5523</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8071</v>
+        <v>4.5485</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4647</v>
+        <v>3.6866</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7125</v>
+        <v>0.5523</v>
       </c>
       <c r="K4" t="n">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="L4" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1772</v>
+        <v>4.2389</v>
       </c>
       <c r="N4" t="n">
-        <v>168</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4994</v>
+        <v>4.6065</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6119</v>
+        <v>1.6503</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3963</v>
+        <v>1.3913</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4994</v>
+        <v>4.6065</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0113</v>
+        <v>2.6421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4881</v>
+        <v>1.9644</v>
       </c>
       <c r="H5" t="n">
-        <v>4.0113</v>
+        <v>2.6421</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2512</v>
+        <v>2.1415</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4881</v>
+        <v>1.9644</v>
       </c>
       <c r="K5" t="n">
-        <v>144</v>
+        <v>44</v>
       </c>
       <c r="L5" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7393</v>
+        <v>4.1059</v>
       </c>
       <c r="N5" t="n">
-        <v>266</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1617</v>
+        <v>4.4994</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4909</v>
+        <v>1.6119</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2599</v>
+        <v>1.3487</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1617</v>
+        <v>4.4994</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1973</v>
+        <v>4.0113</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9644</v>
+        <v>0.4881</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1973</v>
+        <v>4.0113</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7809</v>
+        <v>3.2512</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9644</v>
+        <v>0.4881</v>
       </c>
       <c r="K6" t="n">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="L6" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7453</v>
+        <v>3.7393</v>
       </c>
       <c r="N6" t="n">
-        <v>168</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7">
@@ -732,7 +732,7 @@
         <v>1.4842</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2523</v>
+        <v>1.2067</v>
       </c>
       <c r="E7" t="n">
         <v>4.143</v>
@@ -778,7 +778,7 @@
         <v>1.467</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2329</v>
+        <v>1.1875</v>
       </c>
       <c r="E8" t="n">
         <v>4.095</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1711</v>
+        <v>3.4579</v>
       </c>
       <c r="C9" t="n">
-        <v>1.136</v>
+        <v>1.2388</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8597</v>
+        <v>0.9337</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1711</v>
+        <v>3.4579</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9284</v>
+        <v>2.2152</v>
       </c>
       <c r="G9" t="n">
         <v>1.2427</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9284</v>
+        <v>2.2152</v>
       </c>
       <c r="I9" t="n">
-        <v>1.563</v>
+        <v>1.7955</v>
       </c>
       <c r="J9" t="n">
         <v>1.2427</v>
@@ -851,7 +851,7 @@
         <v>124</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8057</v>
+        <v>3.0382</v>
       </c>
       <c r="N9" t="n">
         <v>168</v>
@@ -870,7 +870,7 @@
         <v>0.9809</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6847</v>
+        <v>0.6469</v>
       </c>
       <c r="E10" t="n">
         <v>2.738</v>
@@ -916,7 +916,7 @@
         <v>0.8316</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5164</v>
+        <v>0.4809</v>
       </c>
       <c r="E11" t="n">
         <v>2.3212</v>
@@ -952,277 +952,277 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0156</v>
+        <v>2.214</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7221</v>
+        <v>0.7932</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3929</v>
+        <v>0.4381</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0156</v>
+        <v>2.214</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0214</v>
+        <v>2.214</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9942</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0214</v>
+        <v>2.214</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8279</v>
+        <v>2.214</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9942</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="L12" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8221</v>
+        <v>2.214</v>
       </c>
       <c r="N12" t="n">
-        <v>168</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7773</v>
+        <v>2.0156</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6367</v>
+        <v>0.7221</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2966</v>
+        <v>0.3591</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7773</v>
+        <v>2.0156</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7773</v>
+        <v>1.0214</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.9942</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7773</v>
+        <v>1.0214</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7773</v>
+        <v>0.8279</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.9942</v>
       </c>
       <c r="K13" t="n">
-        <v>111</v>
+        <v>44</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7773</v>
+        <v>1.8221</v>
       </c>
       <c r="N13" t="n">
-        <v>111</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.6636</v>
+        <v>1.8823</v>
       </c>
       <c r="C14" t="n">
-        <v>0.596</v>
+        <v>0.6743</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2507</v>
+        <v>0.306</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6636</v>
+        <v>1.8823</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7828</v>
+        <v>1.9944</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1192</v>
+        <v>-0.1121</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7828</v>
+        <v>1.9944</v>
       </c>
       <c r="I14" t="n">
-        <v>1.445</v>
+        <v>1.6165</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1192</v>
+        <v>-0.1121</v>
       </c>
       <c r="K14" t="n">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="L14" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3258</v>
+        <v>1.5044</v>
       </c>
       <c r="N14" t="n">
-        <v>220</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6068</v>
+        <v>1.6729</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5756</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2277</v>
+        <v>0.2226</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6068</v>
+        <v>1.6729</v>
       </c>
       <c r="F15" t="n">
-        <v>1.402</v>
+        <v>1.6729</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2048</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.402</v>
+        <v>1.6729</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1364</v>
+        <v>1.6729</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2048</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>166</v>
+        <v>111</v>
       </c>
       <c r="L15" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3412</v>
+        <v>1.6729</v>
       </c>
       <c r="N15" t="n">
-        <v>220</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5429</v>
+        <v>1.6636</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5527</v>
+        <v>0.596</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2019</v>
+        <v>0.2189</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5429</v>
+        <v>1.6636</v>
       </c>
       <c r="F16" t="n">
-        <v>1.655</v>
+        <v>1.7828</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1121</v>
+        <v>-0.1192</v>
       </c>
       <c r="H16" t="n">
-        <v>1.655</v>
+        <v>1.7828</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3414</v>
+        <v>1.445</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1121</v>
+        <v>-0.1192</v>
       </c>
       <c r="K16" t="n">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="L16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2293</v>
+        <v>1.3258</v>
       </c>
       <c r="N16" t="n">
-        <v>118</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2768</v>
+        <v>1.6068</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4574</v>
+        <v>0.5756</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0944</v>
+        <v>0.1962</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2768</v>
+        <v>1.6068</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2768</v>
+        <v>1.402</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.2048</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2768</v>
+        <v>1.402</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2768</v>
+        <v>1.1364</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.2048</v>
       </c>
       <c r="K17" t="n">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2768</v>
+        <v>1.3412</v>
       </c>
       <c r="N17" t="n">
-        <v>113</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9137</v>
+        <v>1.3072</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3273</v>
+        <v>0.4683</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0522</v>
+        <v>0.0769</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9137</v>
+        <v>1.3072</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6807</v>
+        <v>2.0742</v>
       </c>
       <c r="G18" t="n">
         <v>-0.767</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6807</v>
+        <v>2.0742</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3623</v>
+        <v>1.6812</v>
       </c>
       <c r="J18" t="n">
         <v>-0.767</v>
@@ -1265,7 +1265,7 @@
         <v>52</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.9142</v>
       </c>
       <c r="N18" t="n">
         <v>118</v>
@@ -1274,415 +1274,415 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7543</v>
+        <v>1.2768</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2702</v>
+        <v>0.4574</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1166</v>
+        <v>0.0648</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7543</v>
+        <v>1.2768</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7543</v>
+        <v>1.2768</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7543</v>
+        <v>1.2768</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7543</v>
+        <v>1.2768</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7543</v>
+        <v>1.2768</v>
       </c>
       <c r="N19" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7338</v>
+        <v>0.9543</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2629</v>
+        <v>0.3419</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1249</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7338</v>
+        <v>0.9543</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8665</v>
+        <v>0.9543</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1327</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8665</v>
+        <v>0.9543</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7023</v>
+        <v>0.9543</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1327</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="L20" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5696</v>
+        <v>0.9543</v>
       </c>
       <c r="N20" t="n">
-        <v>168</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4307</v>
+        <v>0.7466</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1543</v>
+        <v>0.2675</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2474</v>
+        <v>-0.1465</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4307</v>
+        <v>0.7466</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2765</v>
+        <v>0.8793</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1542</v>
+        <v>-0.1327</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2765</v>
+        <v>0.8793</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2241</v>
+        <v>0.7127</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1542</v>
+        <v>-0.1327</v>
       </c>
       <c r="K21" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="L21" t="n">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3783</v>
+        <v>0.58</v>
       </c>
       <c r="N21" t="n">
-        <v>118</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2265</v>
+        <v>0.4307</v>
       </c>
       <c r="C22" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.1543</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3299</v>
+        <v>-0.2723</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2265</v>
+        <v>0.4307</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2265</v>
+        <v>0.2765</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.1542</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2265</v>
+        <v>0.2765</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2265</v>
+        <v>0.2241</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.1542</v>
       </c>
       <c r="K22" t="n">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2265</v>
+        <v>0.3783</v>
       </c>
       <c r="N22" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2149</v>
+        <v>0.2888</v>
       </c>
       <c r="C23" t="n">
-        <v>0.077</v>
+        <v>0.1035</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3345</v>
+        <v>-0.3289</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2149</v>
+        <v>0.2888</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2149</v>
+        <v>0.2888</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2149</v>
+        <v>0.2888</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2149</v>
+        <v>0.2888</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2149</v>
+        <v>0.2888</v>
       </c>
       <c r="N23" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pimp</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2038</v>
+        <v>0.2265</v>
       </c>
       <c r="C24" t="n">
-        <v>0.073</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.339</v>
+        <v>-0.3537</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2038</v>
+        <v>0.2265</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2038</v>
+        <v>0.2265</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2038</v>
+        <v>0.2265</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2038</v>
+        <v>0.2265</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2038</v>
+        <v>0.2265</v>
       </c>
       <c r="N24" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1232</v>
+        <v>0.2149</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0441</v>
+        <v>0.077</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3716</v>
+        <v>-0.3583</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1232</v>
+        <v>0.2149</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1232</v>
+        <v>0.2149</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1232</v>
+        <v>0.2149</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1232</v>
+        <v>0.2149</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1232</v>
+        <v>0.2149</v>
       </c>
       <c r="N25" t="n">
-        <v>111</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>Pimp</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.2038</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0332</v>
+        <v>0.073</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3839</v>
+        <v>-0.3627</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.2038</v>
       </c>
       <c r="F26" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.2038</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.2038</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.2038</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.2038</v>
       </c>
       <c r="N26" t="n">
-        <v>111</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0441</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0158</v>
+        <v>0.0332</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4035</v>
+        <v>-0.4069</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0441</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0441</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0441</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0441</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0441</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28">
@@ -1698,7 +1698,7 @@
         <v>0.0023</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4188</v>
+        <v>-0.4414</v>
       </c>
       <c r="E28" t="n">
         <v>0.0063</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0883</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.521</v>
+        <v>-0.5422</v>
       </c>
       <c r="E29" t="n">
         <v>-0.2466</v>
@@ -1790,7 +1790,7 @@
         <v>-0.2181</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6673</v>
+        <v>-0.6865</v>
       </c>
       <c r="E30" t="n">
         <v>-0.6088</v>
@@ -1836,7 +1836,7 @@
         <v>-0.2457</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6985</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="E31" t="n">
         <v>-0.6859</v>
@@ -1882,7 +1882,7 @@
         <v>-0.2508</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7042</v>
+        <v>-0.7228</v>
       </c>
       <c r="E32" t="n">
         <v>-0.7000999999999999</v>
@@ -1928,7 +1928,7 @@
         <v>-0.26</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7145</v>
+        <v>-0.733</v>
       </c>
       <c r="E33" t="n">
         <v>-0.7257</v>
@@ -1974,7 +1974,7 @@
         <v>-0.277</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7337</v>
+        <v>-0.752</v>
       </c>
       <c r="E34" t="n">
         <v>-0.7732</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3258</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7887999999999999</v>
+        <v>-0.8063</v>
       </c>
       <c r="E35" t="n">
         <v>-0.9095</v>
@@ -2066,7 +2066,7 @@
         <v>-0.4102</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8839</v>
+        <v>-0.9</v>
       </c>
       <c r="E36" t="n">
         <v>-1.1449</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4211</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8962</v>
+        <v>-0.9122</v>
       </c>
       <c r="E37" t="n">
         <v>-1.1755</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4386</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.916</v>
+        <v>-0.9317</v>
       </c>
       <c r="E38" t="n">
         <v>-1.2244</v>
@@ -2204,7 +2204,7 @@
         <v>-0.5346</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0242</v>
+        <v>-1.0384</v>
       </c>
       <c r="E39" t="n">
         <v>-1.4923</v>
@@ -2250,7 +2250,7 @@
         <v>-0.5765</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0714</v>
+        <v>-1.085</v>
       </c>
       <c r="E40" t="n">
         <v>-1.6092</v>
@@ -2296,7 +2296,7 @@
         <v>-1.2017</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7765</v>
+        <v>-1.7803</v>
       </c>
       <c r="E41" t="n">
         <v>-3.3544</v>

--- a/database/event/1977/event_1977_evp_summary.xlsx
+++ b/database/event/1977/event_1977_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.9375</v>
+        <v>5.2198</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7689</v>
+        <v>1.87</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5232</v>
+        <v>1.7185</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9375</v>
+        <v>5.2198</v>
       </c>
       <c r="F2" t="n">
-        <v>2.225</v>
+        <v>2.5059</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7125</v>
+        <v>2.7139</v>
       </c>
       <c r="H2" t="n">
-        <v>2.225</v>
+        <v>3.343</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8034</v>
+        <v>1.7382</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7125</v>
+        <v>2.7139</v>
       </c>
       <c r="K2" t="n">
         <v>44</v>
@@ -529,7 +529,7 @@
         <v>124</v>
       </c>
       <c r="M2" t="n">
-        <v>4.5159</v>
+        <v>4.4521</v>
       </c>
       <c r="N2" t="n">
         <v>168</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.898</v>
+        <v>5.0389</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7547</v>
+        <v>1.8052</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5075</v>
+        <v>1.6368</v>
       </c>
       <c r="E3" t="n">
-        <v>4.898</v>
+        <v>5.0389</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0775</v>
+        <v>2.7302</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8204</v>
+        <v>2.3087</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0775</v>
+        <v>4.1332</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6839</v>
+        <v>2.1491</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8204</v>
+        <v>2.3087</v>
       </c>
       <c r="K3" t="n">
         <v>144</v>
@@ -575,7 +575,7 @@
         <v>122</v>
       </c>
       <c r="M3" t="n">
-        <v>4.5043</v>
+        <v>4.4578</v>
       </c>
       <c r="N3" t="n">
         <v>266</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8048</v>
+        <v>4.4881</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7213</v>
+        <v>1.6079</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4703</v>
+        <v>1.3881</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8048</v>
+        <v>4.4881</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2525</v>
+        <v>3.8947</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5523</v>
+        <v>0.5934</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5485</v>
+        <v>8.2363</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6866</v>
+        <v>4.2825</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5523</v>
+        <v>0.5934</v>
       </c>
       <c r="K4" t="n">
         <v>144</v>
@@ -621,7 +621,7 @@
         <v>122</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2389</v>
+        <v>4.8759</v>
       </c>
       <c r="N4" t="n">
         <v>266</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6065</v>
+        <v>4.4876</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6503</v>
+        <v>1.6077</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3913</v>
+        <v>1.3879</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6065</v>
+        <v>4.4876</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6421</v>
+        <v>2.7123</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9644</v>
+        <v>1.7753</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6421</v>
+        <v>4.0702</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1415</v>
+        <v>2.1163</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9644</v>
+        <v>1.7753</v>
       </c>
       <c r="K5" t="n">
         <v>44</v>
@@ -667,7 +667,7 @@
         <v>124</v>
       </c>
       <c r="M5" t="n">
-        <v>4.1059</v>
+        <v>3.8916</v>
       </c>
       <c r="N5" t="n">
         <v>168</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4994</v>
+        <v>4.1225</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6119</v>
+        <v>1.4769</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3487</v>
+        <v>1.2231</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4994</v>
+        <v>4.1225</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0113</v>
+        <v>3.5418</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4881</v>
+        <v>0.5807</v>
       </c>
       <c r="H6" t="n">
-        <v>4.0113</v>
+        <v>6.9927</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2512</v>
+        <v>3.6359</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4881</v>
+        <v>0.5807</v>
       </c>
       <c r="K6" t="n">
         <v>144</v>
@@ -713,7 +713,7 @@
         <v>122</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7393</v>
+        <v>4.2166</v>
       </c>
       <c r="N6" t="n">
         <v>266</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.143</v>
+        <v>4.0067</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4842</v>
+        <v>1.4354</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2067</v>
+        <v>1.1708</v>
       </c>
       <c r="E7" t="n">
-        <v>4.143</v>
+        <v>4.0067</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4065</v>
+        <v>3.1777</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7365</v>
+        <v>0.829</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4065</v>
+        <v>5.7099</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7611</v>
+        <v>2.9689</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7365</v>
+        <v>0.829</v>
       </c>
       <c r="K7" t="n">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="L7" t="n">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4976</v>
+        <v>3.7979</v>
       </c>
       <c r="N7" t="n">
-        <v>220</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.095</v>
+        <v>3.897</v>
       </c>
       <c r="C8" t="n">
-        <v>1.467</v>
+        <v>1.3961</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1875</v>
+        <v>1.1213</v>
       </c>
       <c r="E8" t="n">
-        <v>4.095</v>
+        <v>3.897</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2117</v>
+        <v>3.1644</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8833</v>
+        <v>0.7326</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2117</v>
+        <v>5.663</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6031</v>
+        <v>2.9445</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8833</v>
+        <v>0.7326</v>
       </c>
       <c r="K8" t="n">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="L8" t="n">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4864</v>
+        <v>3.6771</v>
       </c>
       <c r="N8" t="n">
-        <v>266</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4579</v>
+        <v>3.5082</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2388</v>
+        <v>1.2568</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9337</v>
+        <v>0.9458</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4579</v>
+        <v>3.5082</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2152</v>
+        <v>2.533</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2427</v>
+        <v>0.9752</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2152</v>
+        <v>3.4386</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7955</v>
+        <v>1.7879</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2427</v>
+        <v>0.9752</v>
       </c>
       <c r="K9" t="n">
         <v>44</v>
@@ -851,7 +851,7 @@
         <v>124</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0382</v>
+        <v>2.7631</v>
       </c>
       <c r="N9" t="n">
         <v>168</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.738</v>
+        <v>3.4056</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9809</v>
+        <v>1.2201</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6469</v>
+        <v>0.8994</v>
       </c>
       <c r="E10" t="n">
-        <v>2.738</v>
+        <v>3.4056</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0117</v>
+        <v>2.6415</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.7641</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0117</v>
+        <v>3.8207</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6306</v>
+        <v>1.9866</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.7641</v>
       </c>
       <c r="K10" t="n">
         <v>166</v>
@@ -897,7 +897,7 @@
         <v>54</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3569</v>
+        <v>2.7507</v>
       </c>
       <c r="N10" t="n">
         <v>220</v>
@@ -906,265 +906,265 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3212</v>
+        <v>2.9498</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8316</v>
+        <v>1.0568</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4809</v>
+        <v>0.6937</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3212</v>
+        <v>2.9498</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3212</v>
+        <v>1.9406</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>1.0092</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3212</v>
+        <v>1.9406</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6919</v>
+        <v>1.009</v>
       </c>
       <c r="J11" t="n">
-        <v>-1</v>
+        <v>1.0092</v>
       </c>
       <c r="K11" t="n">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="L11" t="n">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6919</v>
+        <v>2.0182</v>
       </c>
       <c r="N11" t="n">
-        <v>220</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.214</v>
+        <v>2.6913</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7932</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4381</v>
+        <v>0.577</v>
       </c>
       <c r="E12" t="n">
-        <v>2.214</v>
+        <v>2.6913</v>
       </c>
       <c r="F12" t="n">
-        <v>2.214</v>
+        <v>2.6468</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.0445</v>
       </c>
       <c r="H12" t="n">
-        <v>2.214</v>
+        <v>3.8394</v>
       </c>
       <c r="I12" t="n">
-        <v>2.214</v>
+        <v>1.9963</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.0445</v>
       </c>
       <c r="K12" t="n">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M12" t="n">
-        <v>2.214</v>
+        <v>2.0408</v>
       </c>
       <c r="N12" t="n">
-        <v>111</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0156</v>
+        <v>2.6593</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7221</v>
+        <v>0.9527</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3591</v>
+        <v>0.5625</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0156</v>
+        <v>2.6593</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0214</v>
+        <v>2.422</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9942</v>
+        <v>0.2373</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0214</v>
+        <v>3.0472</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8279</v>
+        <v>1.5844</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9942</v>
+        <v>0.2373</v>
       </c>
       <c r="K13" t="n">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="L13" t="n">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8221</v>
+        <v>1.8217</v>
       </c>
       <c r="N13" t="n">
-        <v>168</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8823</v>
+        <v>2.4804</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6743</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.306</v>
+        <v>0.4818</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8823</v>
+        <v>2.4804</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9944</v>
+        <v>2.4804</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1121</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9944</v>
+        <v>2.4804</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6165</v>
+        <v>2.4804</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1121</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="L14" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5044</v>
+        <v>2.4804</v>
       </c>
       <c r="N14" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6729</v>
+        <v>2.416</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.8655</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2226</v>
+        <v>0.4527</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6729</v>
+        <v>2.416</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6729</v>
+        <v>2.3648</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.0512</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6729</v>
+        <v>2.8456</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6729</v>
+        <v>1.4796</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.0512</v>
       </c>
       <c r="K15" t="n">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6729</v>
+        <v>1.5308</v>
       </c>
       <c r="N15" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6636</v>
+        <v>2.0701</v>
       </c>
       <c r="C16" t="n">
-        <v>0.596</v>
+        <v>0.7416</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2189</v>
+        <v>0.2965</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6636</v>
+        <v>2.0701</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7828</v>
+        <v>3.0701</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1192</v>
+        <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7828</v>
+        <v>5.3309</v>
       </c>
       <c r="I16" t="n">
-        <v>1.445</v>
+        <v>2.7718</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1192</v>
+        <v>-1</v>
       </c>
       <c r="K16" t="n">
         <v>166</v>
@@ -1173,7 +1173,7 @@
         <v>54</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3258</v>
+        <v>1.7718</v>
       </c>
       <c r="N16" t="n">
         <v>220</v>
@@ -1182,47 +1182,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6068</v>
+        <v>1.8573</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5756</v>
+        <v>0.6654</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1962</v>
+        <v>0.2005</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6068</v>
+        <v>1.8573</v>
       </c>
       <c r="F17" t="n">
-        <v>1.402</v>
+        <v>1.8573</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2048</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.402</v>
+        <v>1.8573</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1364</v>
+        <v>1.8573</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2048</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>166</v>
+        <v>111</v>
       </c>
       <c r="L17" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3412</v>
+        <v>1.8573</v>
       </c>
       <c r="N17" t="n">
-        <v>220</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3072</v>
+        <v>1.8431</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4683</v>
+        <v>0.6603</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0769</v>
+        <v>0.1941</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3072</v>
+        <v>1.8431</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0742</v>
+        <v>2.3815</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.767</v>
+        <v>-0.5384</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0742</v>
+        <v>2.9045</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6812</v>
+        <v>1.5102</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.767</v>
+        <v>-0.5384</v>
       </c>
       <c r="K18" t="n">
         <v>66</v>
@@ -1265,7 +1265,7 @@
         <v>52</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9142</v>
+        <v>0.9718</v>
       </c>
       <c r="N18" t="n">
         <v>118</v>
@@ -1274,139 +1274,139 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2768</v>
+        <v>1.2771</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4574</v>
+        <v>0.4575</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0648</v>
+        <v>-0.0615</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2768</v>
+        <v>1.2771</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2768</v>
+        <v>1.5801</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.303</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2768</v>
+        <v>1.5801</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2768</v>
+        <v>0.8216</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.303</v>
       </c>
       <c r="K19" t="n">
-        <v>113</v>
+        <v>44</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2768</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>113</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9543</v>
+        <v>1.2193</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3419</v>
+        <v>0.4368</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.0876</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9543</v>
+        <v>1.2193</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9543</v>
+        <v>1.2193</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9543</v>
+        <v>1.2193</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9543</v>
+        <v>1.2193</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9543</v>
+        <v>1.2193</v>
       </c>
       <c r="N20" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7466</v>
+        <v>1.0532</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2675</v>
+        <v>0.3773</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1465</v>
+        <v>-0.1625</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7466</v>
+        <v>1.0532</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8793</v>
+        <v>1.0532</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1327</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8793</v>
+        <v>1.0532</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7127</v>
+        <v>1.0532</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1327</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="L21" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.58</v>
+        <v>1.0532</v>
       </c>
       <c r="N21" t="n">
-        <v>168</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4307</v>
+        <v>0.8612</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1543</v>
+        <v>0.3085</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2723</v>
+        <v>-0.2492</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4307</v>
+        <v>0.8612</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2765</v>
+        <v>0.6333</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1542</v>
+        <v>0.2279</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2765</v>
+        <v>0.6333</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2241</v>
+        <v>0.3293</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1542</v>
+        <v>0.2279</v>
       </c>
       <c r="K22" t="n">
         <v>66</v>
@@ -1449,7 +1449,7 @@
         <v>52</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3783</v>
+        <v>0.5571999999999999</v>
       </c>
       <c r="N22" t="n">
         <v>118</v>
@@ -1458,32 +1458,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>Spiidi</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2888</v>
+        <v>0.7267</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1035</v>
+        <v>0.2603</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3289</v>
+        <v>-0.3099</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2888</v>
+        <v>0.7267</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2888</v>
+        <v>0.7267</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2888</v>
+        <v>0.7267</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2888</v>
+        <v>0.7267</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2888</v>
+        <v>0.7267</v>
       </c>
       <c r="N23" t="n">
         <v>111</v>
@@ -1504,124 +1504,124 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2265</v>
+        <v>0.6382</v>
       </c>
       <c r="C24" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.2286</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3537</v>
+        <v>-0.3499</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2265</v>
+        <v>0.6382</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2265</v>
+        <v>0.6382</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2265</v>
+        <v>0.6382</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2265</v>
+        <v>0.6382</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2265</v>
+        <v>0.6382</v>
       </c>
       <c r="N24" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2149</v>
+        <v>0.4803</v>
       </c>
       <c r="C25" t="n">
-        <v>0.077</v>
+        <v>0.1721</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3583</v>
+        <v>-0.4212</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2149</v>
+        <v>0.4803</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2149</v>
+        <v>0.927</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.4467</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2149</v>
+        <v>0.927</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2149</v>
+        <v>0.482</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.4467</v>
       </c>
       <c r="K25" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2149</v>
+        <v>0.0353</v>
       </c>
       <c r="N25" t="n">
-        <v>94</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pimp</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2038</v>
+        <v>0.3313</v>
       </c>
       <c r="C26" t="n">
-        <v>0.073</v>
+        <v>0.1187</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3627</v>
+        <v>-0.4884</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2038</v>
+        <v>0.3313</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2038</v>
+        <v>0.3313</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2038</v>
+        <v>0.3313</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2038</v>
+        <v>0.3313</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2038</v>
+        <v>0.3313</v>
       </c>
       <c r="N26" t="n">
         <v>94</v>
@@ -1642,369 +1642,369 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Spiidi</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.3011</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0332</v>
+        <v>0.1079</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4069</v>
+        <v>-0.5021</v>
       </c>
       <c r="E27" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.3011</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.3011</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.3011</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.3011</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.3011</v>
       </c>
       <c r="N27" t="n">
-        <v>111</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0063</v>
+        <v>0.2729</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0023</v>
+        <v>0.0978</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4414</v>
+        <v>-0.5148</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0063</v>
+        <v>0.2729</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0063</v>
+        <v>0.2729</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0063</v>
+        <v>0.2729</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0063</v>
+        <v>0.2729</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0063</v>
+        <v>0.2729</v>
       </c>
       <c r="N28" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>Pimp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2466</v>
+        <v>0.1629</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0883</v>
+        <v>0.0584</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5422</v>
+        <v>-0.5645</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2466</v>
+        <v>0.1629</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4395</v>
+        <v>0.1629</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.6861</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4395</v>
+        <v>0.1629</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3562</v>
+        <v>0.1629</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.6861</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="L29" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3299</v>
+        <v>0.1629</v>
       </c>
       <c r="N29" t="n">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6088</v>
+        <v>-0.2244</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2181</v>
+        <v>-0.0804</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6865</v>
+        <v>-0.7393</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6088</v>
+        <v>-0.2244</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6088</v>
+        <v>-0.2244</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6088</v>
+        <v>-0.2244</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6088</v>
+        <v>-0.2244</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6088</v>
+        <v>-0.2244</v>
       </c>
       <c r="N30" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6859</v>
+        <v>-0.3652</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2457</v>
+        <v>-0.1308</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.8028999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6859</v>
+        <v>-0.3652</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3649</v>
+        <v>-0.3652</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.321</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3649</v>
+        <v>-0.3652</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2958</v>
+        <v>-0.3652</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.321</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="L31" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.6168</v>
+        <v>-0.3652</v>
       </c>
       <c r="N31" t="n">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>Friis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-0.3837</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2508</v>
+        <v>-0.1375</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7228</v>
+        <v>-0.8112</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-0.3837</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-0.3837</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-0.3837</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-0.3837</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-0.3837</v>
       </c>
       <c r="N32" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Friis</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7257</v>
+        <v>-0.3994</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.26</v>
+        <v>-0.1431</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.733</v>
+        <v>-0.8183</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7257</v>
+        <v>-0.3994</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7257</v>
+        <v>-0.3994</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7257</v>
+        <v>-0.3994</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7257</v>
+        <v>-0.3994</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7257</v>
+        <v>-0.3994</v>
       </c>
       <c r="N33" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7732</v>
+        <v>-0.4158</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.277</v>
+        <v>-0.149</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.752</v>
+        <v>-0.8257</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7732</v>
+        <v>-0.4158</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7732</v>
+        <v>-0.3148</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.101</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7732</v>
+        <v>-0.3148</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7732</v>
+        <v>-0.1637</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.101</v>
       </c>
       <c r="K34" t="n">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7732</v>
+        <v>-0.2647</v>
       </c>
       <c r="N34" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9095</v>
+        <v>-0.6087</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3258</v>
+        <v>-0.2181</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8063</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9095</v>
+        <v>-0.6087</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9095</v>
+        <v>-0.6087</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9095</v>
+        <v>-0.6087</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9095</v>
+        <v>-0.6087</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9095</v>
+        <v>-0.6087</v>
       </c>
       <c r="N35" t="n">
         <v>94</v>
@@ -2056,124 +2056,124 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1449</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4102</v>
+        <v>-0.2786</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9</v>
+        <v>-0.9891</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1449</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1449</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1449</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.1449</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1449</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1755</v>
+        <v>-0.7865</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4211</v>
+        <v>-0.2818</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9122</v>
+        <v>-0.9931</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1755</v>
+        <v>-0.7865</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1755</v>
+        <v>-0.7865</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1755</v>
+        <v>-0.7865</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1755</v>
+        <v>-0.7865</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1755</v>
+        <v>-0.7865</v>
       </c>
       <c r="N37" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2244</v>
+        <v>-0.8321</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4386</v>
+        <v>-0.2981</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9317</v>
+        <v>-1.0137</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2244</v>
+        <v>-0.8321</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2244</v>
+        <v>-0.8321</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2244</v>
+        <v>-0.8321</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2244</v>
+        <v>-0.8321</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2244</v>
+        <v>-0.8321</v>
       </c>
       <c r="N38" t="n">
         <v>94</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4923</v>
+        <v>-0.9526</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5346</v>
+        <v>-0.3413</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0384</v>
+        <v>-1.0681</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4923</v>
+        <v>-0.9526</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4923</v>
+        <v>-0.9526</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4923</v>
+        <v>-0.9526</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4923</v>
+        <v>-0.9526</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4923</v>
+        <v>-0.9526</v>
       </c>
       <c r="N39" t="n">
         <v>113</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6092</v>
+        <v>-1.1948</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5765</v>
+        <v>-0.428</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.085</v>
+        <v>-1.1774</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6092</v>
+        <v>-1.1948</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.6092</v>
+        <v>-1.1948</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6092</v>
+        <v>-1.1948</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.6092</v>
+        <v>-1.1948</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.6092</v>
+        <v>-1.1948</v>
       </c>
       <c r="N40" t="n">
         <v>94</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.3544</v>
+        <v>-3.6149</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.2017</v>
+        <v>-1.295</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7803</v>
+        <v>-2.27</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.3544</v>
+        <v>-3.6149</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.1984</v>
+        <v>-2.6945</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.156</v>
+        <v>-0.9204</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.1984</v>
+        <v>-2.6945</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.7819</v>
+        <v>-1.401</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.156</v>
+        <v>-0.9204</v>
       </c>
       <c r="K41" t="n">
         <v>144</v>
@@ -2323,7 +2323,7 @@
         <v>122</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.9379</v>
+        <v>-2.3214</v>
       </c>
       <c r="N41" t="n">
         <v>266</v>
@@ -2429,10 +2429,10 @@
         <v>1.14</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3221</v>
+        <v>0.3511</v>
       </c>
       <c r="J2" t="n">
-        <v>11.2735</v>
+        <v>12.2885</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.92</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.154</v>
+        <v>-0.1042</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.39</v>
+        <v>-3.647</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.89</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2152</v>
+        <v>-0.1368</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.532</v>
+        <v>-4.788</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.86</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2678</v>
+        <v>-0.1685</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.372999999999999</v>
+        <v>-5.8975</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.8</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3628</v>
+        <v>-0.2296</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.698</v>
+        <v>-8.036</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.41</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0763</v>
+        <v>1.0417</v>
       </c>
       <c r="J7" t="n">
-        <v>37.6705</v>
+        <v>36.4595</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5913</v>
+        <v>0.576</v>
       </c>
       <c r="J8" t="n">
-        <v>20.6955</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.17</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.5009</v>
       </c>
       <c r="J9" t="n">
-        <v>17.871</v>
+        <v>17.5315</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2671</v>
+        <v>-0.1973</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.3485</v>
+        <v>-6.9055</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5065</v>
+        <v>-0.4409</v>
       </c>
       <c r="J11" t="n">
-        <v>-17.7275</v>
+        <v>-15.4315</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.13</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2671</v>
+        <v>0.2991</v>
       </c>
       <c r="J12" t="n">
-        <v>9.3485</v>
+        <v>10.4685</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2168</v>
+        <v>0.2399</v>
       </c>
       <c r="J13" t="n">
-        <v>7.588</v>
+        <v>8.3965</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.06</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1425</v>
+        <v>0.1564</v>
       </c>
       <c r="J14" t="n">
-        <v>4.9875</v>
+        <v>5.474</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.01</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0171</v>
+        <v>0.0346</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5985</v>
+        <v>1.211</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.84</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3313</v>
+        <v>-0.2016</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.5955</v>
+        <v>-7.056</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.46</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2011</v>
+        <v>1.1213</v>
       </c>
       <c r="J17" t="n">
-        <v>42.0385</v>
+        <v>39.2455</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.09</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2978</v>
+        <v>0.2979</v>
       </c>
       <c r="J18" t="n">
-        <v>10.423</v>
+        <v>10.4265</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.99</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1311</v>
+        <v>-0.0735</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.5885</v>
+        <v>-2.5725</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.98</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1744</v>
+        <v>-0.1145</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.104</v>
+        <v>-4.0075</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.9</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4361</v>
+        <v>-0.3728</v>
       </c>
       <c r="J21" t="n">
-        <v>-15.2635</v>
+        <v>-13.048</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.31</v>
       </c>
       <c r="I22" t="n">
-        <v>0.87</v>
+        <v>0.638</v>
       </c>
       <c r="J22" t="n">
-        <v>25.23</v>
+        <v>18.502</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4985</v>
+        <v>0.4205</v>
       </c>
       <c r="J23" t="n">
-        <v>14.4565</v>
+        <v>12.1945</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4985</v>
+        <v>0.4205</v>
       </c>
       <c r="J24" t="n">
-        <v>14.4565</v>
+        <v>12.1945</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.07</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2022</v>
+        <v>0.2378</v>
       </c>
       <c r="J25" t="n">
-        <v>5.8638</v>
+        <v>6.8962</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-0.6243</v>
       </c>
       <c r="J26" t="n">
-        <v>-19.6881</v>
+        <v>-18.1047</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.3</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4875</v>
+        <v>0.4814</v>
       </c>
       <c r="J27" t="n">
-        <v>14.1375</v>
+        <v>13.9606</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.2</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3486</v>
+        <v>0.3799</v>
       </c>
       <c r="J28" t="n">
-        <v>10.1094</v>
+        <v>11.0171</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.13</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2375</v>
+        <v>0.2847</v>
       </c>
       <c r="J29" t="n">
-        <v>6.8875</v>
+        <v>8.2563</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.12</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2198</v>
+        <v>0.2659</v>
       </c>
       <c r="J30" t="n">
-        <v>6.3742</v>
+        <v>7.7111</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4716</v>
+        <v>-0.2991</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.6764</v>
+        <v>-8.6739</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.52</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2271</v>
+        <v>0.8767</v>
       </c>
       <c r="J32" t="n">
-        <v>30.6775</v>
+        <v>21.9175</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.31</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7709</v>
+        <v>0.608</v>
       </c>
       <c r="J33" t="n">
-        <v>19.2725</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.27</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6575</v>
+        <v>0.556</v>
       </c>
       <c r="J34" t="n">
-        <v>16.4375</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.15</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3405</v>
+        <v>0.3855</v>
       </c>
       <c r="J35" t="n">
-        <v>8.512499999999999</v>
+        <v>9.637499999999999</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.11</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2329</v>
+        <v>0.3131</v>
       </c>
       <c r="J36" t="n">
-        <v>5.8225</v>
+        <v>7.8275</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.16</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3777</v>
+        <v>0.3842</v>
       </c>
       <c r="J37" t="n">
-        <v>9.442500000000001</v>
+        <v>9.605</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.08</v>
       </c>
       <c r="I38" t="n">
-        <v>0.249</v>
+        <v>0.2512</v>
       </c>
       <c r="J38" t="n">
-        <v>6.225</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.96</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0327</v>
+        <v>-0.0474</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8175</v>
+        <v>-1.185</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.8</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.339</v>
+        <v>-0.2214</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.475</v>
+        <v>-5.535</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.28</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.995</v>
+        <v>-0.7018</v>
       </c>
       <c r="J41" t="n">
-        <v>-24.875</v>
+        <v>-17.545</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.14</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3496</v>
+        <v>0.3621</v>
       </c>
       <c r="J42" t="n">
-        <v>8.3904</v>
+        <v>8.6904</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.93</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.1456</v>
+        <v>-2.028</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.82</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3027</v>
+        <v>-0.201</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.2648</v>
+        <v>-4.824</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.75</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4139</v>
+        <v>-0.2695</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.9336</v>
+        <v>-6.468</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.61</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6066</v>
+        <v>-0.4023</v>
       </c>
       <c r="J46" t="n">
-        <v>-14.5584</v>
+        <v>-9.655200000000001</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.77</v>
       </c>
       <c r="I47" t="n">
-        <v>1.7178</v>
+        <v>1.2054</v>
       </c>
       <c r="J47" t="n">
-        <v>41.2272</v>
+        <v>28.9296</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.31</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8165</v>
+        <v>0.6186</v>
       </c>
       <c r="J48" t="n">
-        <v>19.596</v>
+        <v>14.8464</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.06</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1165</v>
+        <v>0.1846</v>
       </c>
       <c r="J49" t="n">
-        <v>2.796</v>
+        <v>4.4304</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1226</v>
+        <v>-0.0481</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.9424</v>
+        <v>-1.1544</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.85</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6073</v>
+        <v>-0.5427</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.5752</v>
+        <v>-13.0248</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3018</v>
+        <v>0.3207</v>
       </c>
       <c r="J52" t="n">
-        <v>8.4504</v>
+        <v>8.9796</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.11</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2856</v>
+        <v>0.3013</v>
       </c>
       <c r="J53" t="n">
-        <v>7.9968</v>
+        <v>8.436400000000001</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1954</v>
+        <v>-0.1342</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.4712</v>
+        <v>-3.7576</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.78</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3834</v>
+        <v>-0.2457</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.7352</v>
+        <v>-6.8796</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6776</v>
+        <v>-0.4539</v>
       </c>
       <c r="J56" t="n">
-        <v>-18.9728</v>
+        <v>-12.7092</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.38</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9871</v>
+        <v>0.7176</v>
       </c>
       <c r="J57" t="n">
-        <v>27.6388</v>
+        <v>20.0928</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.23</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6374</v>
+        <v>0.5123</v>
       </c>
       <c r="J58" t="n">
-        <v>17.8472</v>
+        <v>14.3444</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.22</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.4982</v>
       </c>
       <c r="J59" t="n">
-        <v>17.1192</v>
+        <v>13.9496</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.09</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2211</v>
+        <v>0.2806</v>
       </c>
       <c r="J60" t="n">
-        <v>6.1908</v>
+        <v>7.8568</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3506</v>
+        <v>-0.2755</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.816800000000001</v>
+        <v>-7.714</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.75</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2896</v>
+        <v>-0.2394</v>
       </c>
       <c r="J62" t="n">
-        <v>-5.792</v>
+        <v>-4.788</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3853</v>
+        <v>-0.2991</v>
       </c>
       <c r="J63" t="n">
-        <v>-7.706</v>
+        <v>-5.982</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.68</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4019</v>
+        <v>-0.3086</v>
       </c>
       <c r="J64" t="n">
-        <v>-8.038</v>
+        <v>-6.172</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.63</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5013</v>
+        <v>-0.3531</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.026</v>
+        <v>-7.062</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.48</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7227</v>
+        <v>-0.4924</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.454</v>
+        <v>-9.848000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.63</v>
       </c>
       <c r="I67" t="n">
-        <v>1.3278</v>
+        <v>1.2418</v>
       </c>
       <c r="J67" t="n">
-        <v>26.556</v>
+        <v>24.836</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.53</v>
       </c>
       <c r="I68" t="n">
-        <v>1.117</v>
+        <v>1.127</v>
       </c>
       <c r="J68" t="n">
-        <v>22.34</v>
+        <v>22.54</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.49</v>
       </c>
       <c r="I69" t="n">
-        <v>1.0144</v>
+        <v>1.0812</v>
       </c>
       <c r="J69" t="n">
-        <v>20.288</v>
+        <v>21.624</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.48</v>
       </c>
       <c r="I70" t="n">
-        <v>0.9921</v>
+        <v>1.0694</v>
       </c>
       <c r="J70" t="n">
-        <v>19.842</v>
+        <v>21.388</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.47</v>
       </c>
       <c r="I71" t="n">
-        <v>0.9702</v>
+        <v>1.0573</v>
       </c>
       <c r="J71" t="n">
-        <v>19.404</v>
+        <v>21.146</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.48</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7161</v>
+        <v>0.8869</v>
       </c>
       <c r="J72" t="n">
-        <v>20.7669</v>
+        <v>25.7201</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6334</v>
+        <v>0.7739</v>
       </c>
       <c r="J73" t="n">
-        <v>18.3686</v>
+        <v>22.4431</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.96</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1409</v>
+        <v>-0.0709</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.0861</v>
+        <v>-2.0561</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2966</v>
+        <v>-0.1753</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.6014</v>
+        <v>-5.0837</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.66</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.583</v>
+        <v>-0.3817</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.907</v>
+        <v>-11.0693</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.3</v>
       </c>
       <c r="I77" t="n">
-        <v>0.836</v>
+        <v>0.8187</v>
       </c>
       <c r="J77" t="n">
-        <v>24.244</v>
+        <v>23.7423</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.2</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5926</v>
+        <v>0.5766</v>
       </c>
       <c r="J78" t="n">
-        <v>17.1854</v>
+        <v>16.7214</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.19</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5663</v>
+        <v>0.5517</v>
       </c>
       <c r="J79" t="n">
-        <v>16.4227</v>
+        <v>15.9993</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.07</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1881</v>
+        <v>0.2335</v>
       </c>
       <c r="J80" t="n">
-        <v>5.4549</v>
+        <v>6.7715</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.85</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5849</v>
+        <v>-0.5232</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.9621</v>
+        <v>-15.1728</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.0577</v>
       </c>
       <c r="J82" t="n">
-        <v>2.2011</v>
+        <v>1.3271</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.99</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0612</v>
+        <v>0.0175</v>
       </c>
       <c r="J83" t="n">
-        <v>1.4076</v>
+        <v>0.4025</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.85</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2073</v>
+        <v>-0.1657</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.7679</v>
+        <v>-3.8111</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.68</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4978</v>
+        <v>-0.3292</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.4494</v>
+        <v>-7.5716</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.47</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>-17.7261</v>
+        <v>-12.0681</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.5</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1755</v>
+        <v>1.1208</v>
       </c>
       <c r="J87" t="n">
-        <v>27.0365</v>
+        <v>25.7784</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.43</v>
       </c>
       <c r="I88" t="n">
-        <v>1.0301</v>
+        <v>1.0306</v>
       </c>
       <c r="J88" t="n">
-        <v>23.6923</v>
+        <v>23.7038</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.38</v>
       </c>
       <c r="I89" t="n">
-        <v>0.9206</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>21.1738</v>
+        <v>21.7373</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.19</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4328</v>
+        <v>0.5177</v>
       </c>
       <c r="J90" t="n">
-        <v>9.9544</v>
+        <v>11.9071</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.98</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2537</v>
+        <v>-0.168</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.8351</v>
+        <v>-3.864</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.92</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.0224</v>
+        <v>-0.0519</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.4704</v>
+        <v>-1.0899</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.73</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.3327</v>
+        <v>-0.2641</v>
       </c>
       <c r="J93" t="n">
-        <v>-6.9867</v>
+        <v>-5.5461</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.7</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3818</v>
+        <v>-0.2931</v>
       </c>
       <c r="J94" t="n">
-        <v>-8.017799999999999</v>
+        <v>-6.1551</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.6</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.5615</v>
+        <v>-0.3836</v>
       </c>
       <c r="J95" t="n">
-        <v>-11.7915</v>
+        <v>-8.0556</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.38</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.8555</v>
+        <v>-0.5899</v>
       </c>
       <c r="J96" t="n">
-        <v>-17.9655</v>
+        <v>-12.3879</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>1.9724</v>
+        <v>1.6734</v>
       </c>
       <c r="J97" t="n">
-        <v>41.4204</v>
+        <v>35.1414</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.99</v>
       </c>
       <c r="I98" t="n">
-        <v>1.9622</v>
+        <v>1.6622</v>
       </c>
       <c r="J98" t="n">
-        <v>41.2062</v>
+        <v>34.9062</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.45</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9671999999999999</v>
+        <v>1.0375</v>
       </c>
       <c r="J99" t="n">
-        <v>20.3112</v>
+        <v>21.7875</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.19</v>
       </c>
       <c r="I100" t="n">
-        <v>0.375</v>
+        <v>0.4833</v>
       </c>
       <c r="J100" t="n">
-        <v>7.875</v>
+        <v>10.1493</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.65</v>
       </c>
       <c r="I101" t="n">
-        <v>-1.0986</v>
+        <v>-1.0893</v>
       </c>
       <c r="J101" t="n">
-        <v>-23.0706</v>
+        <v>-22.8753</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.42</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6092</v>
+        <v>0.536</v>
       </c>
       <c r="J102" t="n">
-        <v>16.4484</v>
+        <v>14.472</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.28</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4291</v>
+        <v>0.3764</v>
       </c>
       <c r="J103" t="n">
-        <v>11.5857</v>
+        <v>10.1628</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.22</v>
       </c>
       <c r="I104" t="n">
-        <v>0.341</v>
+        <v>0.3056</v>
       </c>
       <c r="J104" t="n">
-        <v>9.207000000000001</v>
+        <v>8.251200000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.06</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0674</v>
+        <v>0.0931</v>
       </c>
       <c r="J105" t="n">
-        <v>1.8198</v>
+        <v>2.5137</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0183</v>
       </c>
       <c r="J106" t="n">
-        <v>-1.89</v>
+        <v>-0.4941</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.11</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2704</v>
+        <v>0.2194</v>
       </c>
       <c r="J107" t="n">
-        <v>7.3008</v>
+        <v>5.9238</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.08</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2194</v>
+        <v>0.171</v>
       </c>
       <c r="J108" t="n">
-        <v>5.9238</v>
+        <v>4.617</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.98</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0222</v>
+        <v>-0.0303</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.5994</v>
+        <v>-0.8181</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4382</v>
+        <v>-0.2801</v>
       </c>
       <c r="J110" t="n">
-        <v>-11.8314</v>
+        <v>-7.5627</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.74</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4522</v>
+        <v>-0.2898</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.2094</v>
+        <v>-7.8246</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.06</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2113</v>
+        <v>0.204</v>
       </c>
       <c r="J112" t="n">
-        <v>4.8599</v>
+        <v>4.692</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0747</v>
+        <v>-0.0738</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.7181</v>
+        <v>-1.6974</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.91</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1318</v>
+        <v>-0.1093</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.0314</v>
+        <v>-2.5139</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.71</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4748</v>
+        <v>-0.3093</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.9204</v>
+        <v>-7.1139</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.68</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5163</v>
+        <v>-0.3379</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.8749</v>
+        <v>-7.7717</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.45</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0775</v>
+        <v>1.0597</v>
       </c>
       <c r="J117" t="n">
-        <v>24.7825</v>
+        <v>24.3731</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.39</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9485</v>
+        <v>0.9665</v>
       </c>
       <c r="J118" t="n">
-        <v>21.8155</v>
+        <v>22.2295</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.24</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5644</v>
+        <v>0.6402</v>
       </c>
       <c r="J119" t="n">
-        <v>12.9812</v>
+        <v>14.7246</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.21</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4883</v>
+        <v>0.5689</v>
       </c>
       <c r="J120" t="n">
-        <v>11.2309</v>
+        <v>13.0847</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.14</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3082</v>
+        <v>0.3918</v>
       </c>
       <c r="J121" t="n">
-        <v>7.0886</v>
+        <v>9.0114</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.11</v>
       </c>
       <c r="I122" t="n">
-        <v>0.241</v>
+        <v>0.2641</v>
       </c>
       <c r="J122" t="n">
-        <v>10.122</v>
+        <v>11.0922</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.11</v>
       </c>
       <c r="I123" t="n">
-        <v>0.241</v>
+        <v>0.2641</v>
       </c>
       <c r="J123" t="n">
-        <v>10.122</v>
+        <v>11.0922</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.98</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0731</v>
+        <v>-0.0368</v>
       </c>
       <c r="J124" t="n">
-        <v>-3.0702</v>
+        <v>-1.5456</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.96</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1187</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="J125" t="n">
-        <v>-4.9854</v>
+        <v>-2.6964</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.89</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2478</v>
+        <v>-0.1464</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.4076</v>
+        <v>-6.1488</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.52</v>
       </c>
       <c r="I127" t="n">
-        <v>1.2759</v>
+        <v>1.1743</v>
       </c>
       <c r="J127" t="n">
-        <v>53.5878</v>
+        <v>49.3206</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.4</v>
       </c>
       <c r="I128" t="n">
-        <v>1.0301</v>
+        <v>1.0128</v>
       </c>
       <c r="J128" t="n">
-        <v>43.2642</v>
+        <v>42.5376</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.08</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1908</v>
+        <v>0.2515</v>
       </c>
       <c r="J129" t="n">
-        <v>8.0136</v>
+        <v>10.563</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.02</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0114</v>
+        <v>0.0544</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.4788</v>
+        <v>2.2848</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.84</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6253</v>
+        <v>-0.5631</v>
       </c>
       <c r="J131" t="n">
-        <v>-26.2626</v>
+        <v>-23.6502</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.39</v>
       </c>
       <c r="I132" t="n">
-        <v>0.992</v>
+        <v>0.9868</v>
       </c>
       <c r="J132" t="n">
-        <v>22.816</v>
+        <v>22.6964</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.34</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8818</v>
+        <v>0.8837</v>
       </c>
       <c r="J133" t="n">
-        <v>20.2814</v>
+        <v>20.3251</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.26</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6924</v>
+        <v>0.6999</v>
       </c>
       <c r="J134" t="n">
-        <v>15.9252</v>
+        <v>16.0977</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.1</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2343</v>
+        <v>0.3016</v>
       </c>
       <c r="J135" t="n">
-        <v>5.3889</v>
+        <v>6.9368</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.93</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3915</v>
+        <v>-0.3149</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.0045</v>
+        <v>-7.2427</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.04</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1742</v>
+        <v>0.1573</v>
       </c>
       <c r="J137" t="n">
-        <v>4.0066</v>
+        <v>3.6179</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.95</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0531</v>
+        <v>-0.0606</v>
       </c>
       <c r="J138" t="n">
-        <v>-1.2213</v>
+        <v>-1.3938</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.89</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.167</v>
+        <v>-0.1309</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.841</v>
+        <v>-3.0107</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.73</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4452</v>
+        <v>-0.2896</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.2396</v>
+        <v>-6.6608</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.67</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5288</v>
+        <v>-0.3468</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.1624</v>
+        <v>-7.9764</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.14</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3303</v>
+        <v>0.2752</v>
       </c>
       <c r="J142" t="n">
-        <v>8.5878</v>
+        <v>7.1552</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0529</v>
+        <v>0.0159</v>
       </c>
       <c r="J143" t="n">
-        <v>1.3754</v>
+        <v>0.4134</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0939</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.4414</v>
+        <v>-2.0592</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.84</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2922</v>
+        <v>-0.1866</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.5972</v>
+        <v>-4.8516</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.58</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6544</v>
+        <v>-0.4364</v>
       </c>
       <c r="J146" t="n">
-        <v>-17.0144</v>
+        <v>-11.3464</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.42</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6163</v>
+        <v>0.5407</v>
       </c>
       <c r="J147" t="n">
-        <v>16.0238</v>
+        <v>14.0582</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.16</v>
       </c>
       <c r="I148" t="n">
-        <v>0.246</v>
+        <v>0.2352</v>
       </c>
       <c r="J148" t="n">
-        <v>6.396</v>
+        <v>6.1152</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.13</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1948</v>
+        <v>0.1965</v>
       </c>
       <c r="J149" t="n">
-        <v>5.0648</v>
+        <v>5.109</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.09</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1271</v>
+        <v>0.1411</v>
       </c>
       <c r="J150" t="n">
-        <v>3.3046</v>
+        <v>3.6686</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.06</v>
       </c>
       <c r="I151" t="n">
-        <v>0.0738</v>
+        <v>0.096</v>
       </c>
       <c r="J151" t="n">
-        <v>1.9188</v>
+        <v>2.496</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.42</v>
       </c>
       <c r="I152" t="n">
-        <v>1.0325</v>
+        <v>1.025</v>
       </c>
       <c r="J152" t="n">
-        <v>26.845</v>
+        <v>26.65</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.42</v>
       </c>
       <c r="I153" t="n">
-        <v>1.0325</v>
+        <v>1.025</v>
       </c>
       <c r="J153" t="n">
-        <v>26.845</v>
+        <v>26.65</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.39</v>
       </c>
       <c r="I154" t="n">
-        <v>0.9679</v>
+        <v>0.9749</v>
       </c>
       <c r="J154" t="n">
-        <v>25.1654</v>
+        <v>25.3474</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.24</v>
       </c>
       <c r="I155" t="n">
-        <v>0.5913</v>
+        <v>0.6463</v>
       </c>
       <c r="J155" t="n">
-        <v>15.3738</v>
+        <v>16.8038</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.78</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7879</v>
+        <v>-0.7377</v>
       </c>
       <c r="J156" t="n">
-        <v>-20.4854</v>
+        <v>-19.1802</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.02</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1568</v>
+        <v>0.1303</v>
       </c>
       <c r="J157" t="n">
-        <v>4.0768</v>
+        <v>3.3878</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.85</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.2052</v>
+        <v>-0.1651</v>
       </c>
       <c r="J158" t="n">
-        <v>-5.3352</v>
+        <v>-4.2926</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.84</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2224</v>
+        <v>-0.1755</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.7824</v>
+        <v>-4.563</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.73</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4224</v>
+        <v>-0.2812</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.9824</v>
+        <v>-7.3112</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.53</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.4689</v>
       </c>
       <c r="J161" t="n">
-        <v>-18.0986</v>
+        <v>-12.1914</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.33</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5354</v>
+        <v>0.643</v>
       </c>
       <c r="J162" t="n">
-        <v>21.9514</v>
+        <v>26.363</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.32</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5225</v>
+        <v>0.6262</v>
       </c>
       <c r="J163" t="n">
-        <v>21.4225</v>
+        <v>25.6742</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.03</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0466</v>
+        <v>0.082</v>
       </c>
       <c r="J164" t="n">
-        <v>1.9106</v>
+        <v>3.362</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.85</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3262</v>
+        <v>-0.196</v>
       </c>
       <c r="J165" t="n">
-        <v>-13.3742</v>
+        <v>-8.036</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3558</v>
+        <v>-0.2167</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.5878</v>
+        <v>-8.8847</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.08</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3367</v>
+        <v>0.2908</v>
       </c>
       <c r="J167" t="n">
-        <v>13.8047</v>
+        <v>11.9228</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.07</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3048</v>
+        <v>0.2606</v>
       </c>
       <c r="J168" t="n">
-        <v>12.4968</v>
+        <v>10.6846</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.99</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.068</v>
+        <v>-0.053</v>
       </c>
       <c r="J169" t="n">
-        <v>-2.788</v>
+        <v>-2.173</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.95</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2342</v>
+        <v>-0.1967</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.6022</v>
+        <v>-8.0647</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.9</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3954</v>
+        <v>-0.3483</v>
       </c>
       <c r="J171" t="n">
-        <v>-16.2114</v>
+        <v>-14.2803</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.41</v>
       </c>
       <c r="I172" t="n">
-        <v>1.0173</v>
+        <v>1.0122</v>
       </c>
       <c r="J172" t="n">
-        <v>25.4325</v>
+        <v>25.305</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.27</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.7157</v>
       </c>
       <c r="J173" t="n">
-        <v>17.3525</v>
+        <v>17.8925</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.24</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6096</v>
+        <v>0.6476</v>
       </c>
       <c r="J174" t="n">
-        <v>15.24</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.16</v>
       </c>
       <c r="I175" t="n">
-        <v>0.3834</v>
+        <v>0.4547</v>
       </c>
       <c r="J175" t="n">
-        <v>9.585000000000001</v>
+        <v>11.3675</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.11</v>
       </c>
       <c r="I176" t="n">
-        <v>0.247</v>
+        <v>0.3216</v>
       </c>
       <c r="J176" t="n">
-        <v>6.175</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.13</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3355</v>
+        <v>0.3629</v>
       </c>
       <c r="J177" t="n">
-        <v>8.387499999999999</v>
+        <v>9.0725</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.96</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0283</v>
+        <v>-0.0457</v>
       </c>
       <c r="J178" t="n">
-        <v>-0.7075</v>
+        <v>-1.1425</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.79</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3507</v>
+        <v>-0.23</v>
       </c>
       <c r="J179" t="n">
-        <v>-8.7675</v>
+        <v>-5.75</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.74</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4273</v>
+        <v>-0.2786</v>
       </c>
       <c r="J180" t="n">
-        <v>-10.6825</v>
+        <v>-6.965</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.61</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6057</v>
+        <v>-0.4018</v>
       </c>
       <c r="J181" t="n">
-        <v>-15.1425</v>
+        <v>-10.045</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.61</v>
       </c>
       <c r="I182" t="n">
-        <v>1.3764</v>
+        <v>1.2496</v>
       </c>
       <c r="J182" t="n">
-        <v>34.41</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.56</v>
       </c>
       <c r="I183" t="n">
-        <v>1.2798</v>
+        <v>1.1888</v>
       </c>
       <c r="J183" t="n">
-        <v>31.995</v>
+        <v>29.72</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.26</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5904</v>
+        <v>0.6787</v>
       </c>
       <c r="J184" t="n">
-        <v>14.76</v>
+        <v>16.9675</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.14</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2921</v>
+        <v>0.3823</v>
       </c>
       <c r="J185" t="n">
-        <v>7.3025</v>
+        <v>9.557499999999999</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.07</v>
       </c>
       <c r="I186" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1846</v>
       </c>
       <c r="J186" t="n">
-        <v>2.49</v>
+        <v>4.615</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.88</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1287</v>
+        <v>-0.1223</v>
       </c>
       <c r="J187" t="n">
-        <v>-3.2175</v>
+        <v>-3.0575</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.85</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.179</v>
+        <v>-0.1557</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.475</v>
+        <v>-3.8925</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.73</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3936</v>
+        <v>-0.2746</v>
       </c>
       <c r="J189" t="n">
-        <v>-9.84</v>
+        <v>-6.865</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.68</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4759</v>
+        <v>-0.321</v>
       </c>
       <c r="J190" t="n">
-        <v>-11.8975</v>
+        <v>-8.025</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.57</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.424</v>
       </c>
       <c r="J191" t="n">
-        <v>-15.79</v>
+        <v>-10.6</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.01</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2153</v>
+        <v>0.2152</v>
       </c>
       <c r="J192" t="n">
-        <v>4.5213</v>
+        <v>4.5192</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.3689</v>
+        <v>-0.2938</v>
       </c>
       <c r="J193" t="n">
-        <v>-7.7469</v>
+        <v>-6.1698</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.62</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.4932</v>
+        <v>-0.3589</v>
       </c>
       <c r="J194" t="n">
-        <v>-10.3572</v>
+        <v>-7.5369</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.52</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.6582</v>
+        <v>-0.45</v>
       </c>
       <c r="J195" t="n">
-        <v>-13.8222</v>
+        <v>-9.449999999999999</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.26</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.6973</v>
       </c>
       <c r="J196" t="n">
-        <v>-20.8404</v>
+        <v>-14.6433</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>2.04</v>
       </c>
       <c r="I197" t="n">
-        <v>1.9945</v>
+        <v>1.7014</v>
       </c>
       <c r="J197" t="n">
-        <v>41.8845</v>
+        <v>35.7294</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.6</v>
       </c>
       <c r="I198" t="n">
-        <v>1.265</v>
+        <v>1.2067</v>
       </c>
       <c r="J198" t="n">
-        <v>26.565</v>
+        <v>25.3407</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.45</v>
       </c>
       <c r="I199" t="n">
-        <v>0.9241</v>
+        <v>1.0306</v>
       </c>
       <c r="J199" t="n">
-        <v>19.4061</v>
+        <v>21.6426</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.27</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5379</v>
+        <v>0.6619</v>
       </c>
       <c r="J200" t="n">
-        <v>11.2959</v>
+        <v>13.8999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.27</v>
       </c>
       <c r="I201" t="n">
-        <v>0.5379</v>
+        <v>0.6619</v>
       </c>
       <c r="J201" t="n">
-        <v>11.2959</v>
+        <v>13.8999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.13</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3411</v>
+        <v>0.3698</v>
       </c>
       <c r="J202" t="n">
-        <v>8.5275</v>
+        <v>9.244999999999999</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.92</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0998</v>
+        <v>-0.0935</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.495</v>
+        <v>-2.3375</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.76</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.392</v>
+        <v>-0.2574</v>
       </c>
       <c r="J204" t="n">
-        <v>-9.800000000000001</v>
+        <v>-6.435</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.75</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4073</v>
+        <v>-0.2671</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.1825</v>
+        <v>-6.6775</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.6</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.4092</v>
       </c>
       <c r="J206" t="n">
-        <v>-15.385</v>
+        <v>-10.23</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.94</v>
       </c>
       <c r="I207" t="n">
-        <v>1.9558</v>
+        <v>1.6536</v>
       </c>
       <c r="J207" t="n">
-        <v>48.895</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.22</v>
       </c>
       <c r="I208" t="n">
-        <v>0.5147</v>
+        <v>0.5934</v>
       </c>
       <c r="J208" t="n">
-        <v>12.8675</v>
+        <v>14.835</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.2</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4639</v>
+        <v>0.545</v>
       </c>
       <c r="J209" t="n">
-        <v>11.5975</v>
+        <v>13.625</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.13</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2824</v>
+        <v>0.3656</v>
       </c>
       <c r="J210" t="n">
-        <v>7.06</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.93</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4144</v>
+        <v>-0.3342</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.36</v>
+        <v>-8.355</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.65</v>
       </c>
       <c r="I212" t="n">
-        <v>1.42</v>
+        <v>1.2835</v>
       </c>
       <c r="J212" t="n">
-        <v>26.98</v>
+        <v>24.3865</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.53</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1859</v>
+        <v>1.1403</v>
       </c>
       <c r="J213" t="n">
-        <v>22.5321</v>
+        <v>21.6657</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.5</v>
       </c>
       <c r="I214" t="n">
-        <v>1.1242</v>
+        <v>1.1041</v>
       </c>
       <c r="J214" t="n">
-        <v>21.3598</v>
+        <v>20.9779</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.27</v>
       </c>
       <c r="I215" t="n">
-        <v>0.5809</v>
+        <v>0.6874</v>
       </c>
       <c r="J215" t="n">
-        <v>11.0371</v>
+        <v>13.0606</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.05</v>
       </c>
       <c r="I216" t="n">
-        <v>0.0186</v>
+        <v>0.1059</v>
       </c>
       <c r="J216" t="n">
-        <v>0.3534</v>
+        <v>2.0121</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.88</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.1033</v>
       </c>
       <c r="J217" t="n">
-        <v>-1.7993</v>
+        <v>-1.9627</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.84</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.1607</v>
+        <v>-0.1496</v>
       </c>
       <c r="J218" t="n">
-        <v>-3.0533</v>
+        <v>-2.8424</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.71</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.369</v>
+        <v>-0.2847</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.011</v>
+        <v>-5.4093</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.57</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.608</v>
+        <v>-0.4125</v>
       </c>
       <c r="J220" t="n">
-        <v>-11.552</v>
+        <v>-7.8375</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.36</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.881</v>
+        <v>-0.6096</v>
       </c>
       <c r="J221" t="n">
-        <v>-16.739</v>
+        <v>-11.5824</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1977/event_1977_evp_summary.xlsx
+++ b/database/event/1977/event_1977_evp_summary.xlsx
@@ -492,185 +492,185 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.2198</v>
+        <v>5.1102</v>
       </c>
       <c r="C2" t="n">
-        <v>1.87</v>
+        <v>1.8307</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7185</v>
+        <v>1.7021</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2198</v>
+        <v>5.1102</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5059</v>
+        <v>2.6334</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7139</v>
+        <v>2.4768</v>
       </c>
       <c r="H2" t="n">
-        <v>3.343</v>
+        <v>3.7945</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7382</v>
+        <v>2.049</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7139</v>
+        <v>2.4768</v>
       </c>
       <c r="K2" t="n">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="L2" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M2" t="n">
-        <v>4.4521</v>
+        <v>4.5258</v>
       </c>
       <c r="N2" t="n">
-        <v>168</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.0389</v>
+        <v>5.1083</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8052</v>
+        <v>1.8301</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6368</v>
+        <v>1.7012</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0389</v>
+        <v>5.1083</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7302</v>
+        <v>2.4463</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3087</v>
+        <v>2.662</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1332</v>
+        <v>3.1771</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1491</v>
+        <v>1.7156</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3087</v>
+        <v>2.662</v>
       </c>
       <c r="K3" t="n">
-        <v>144</v>
+        <v>44</v>
       </c>
       <c r="L3" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4578</v>
+        <v>4.3776</v>
       </c>
       <c r="N3" t="n">
-        <v>266</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4881</v>
+        <v>4.4912</v>
       </c>
       <c r="C4" t="n">
-        <v>1.6079</v>
+        <v>1.609</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3881</v>
+        <v>1.4203</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4881</v>
+        <v>4.4912</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8947</v>
+        <v>2.6227</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5934</v>
+        <v>1.8685</v>
       </c>
       <c r="H4" t="n">
-        <v>8.2363</v>
+        <v>3.7589</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2825</v>
+        <v>2.0298</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5934</v>
+        <v>1.8685</v>
       </c>
       <c r="K4" t="n">
-        <v>144</v>
+        <v>44</v>
       </c>
       <c r="L4" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M4" t="n">
-        <v>4.8759</v>
+        <v>3.8983</v>
       </c>
       <c r="N4" t="n">
-        <v>266</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4876</v>
+        <v>4.4235</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6077</v>
+        <v>1.5847</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3879</v>
+        <v>1.3895</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4876</v>
+        <v>4.4235</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7123</v>
+        <v>3.7811</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7753</v>
+        <v>0.6424</v>
       </c>
       <c r="H5" t="n">
-        <v>4.0702</v>
+        <v>7.5812</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1163</v>
+        <v>4.0938</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7753</v>
+        <v>0.6424</v>
       </c>
       <c r="K5" t="n">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="L5" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8916</v>
+        <v>4.7362</v>
       </c>
       <c r="N5" t="n">
-        <v>168</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1225</v>
+        <v>4.1158</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4769</v>
+        <v>1.4745</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2231</v>
+        <v>1.2494</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1225</v>
+        <v>4.1158</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5418</v>
+        <v>3.4769</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5807</v>
+        <v>0.6389</v>
       </c>
       <c r="H6" t="n">
-        <v>6.9927</v>
+        <v>6.5775</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6359</v>
+        <v>3.5518</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5807</v>
+        <v>0.6389</v>
       </c>
       <c r="K6" t="n">
         <v>144</v>
@@ -713,7 +713,7 @@
         <v>122</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2166</v>
+        <v>4.1907</v>
       </c>
       <c r="N6" t="n">
         <v>266</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0067</v>
+        <v>3.9626</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4354</v>
+        <v>1.4196</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1708</v>
+        <v>1.1797</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0067</v>
+        <v>3.9626</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1777</v>
+        <v>3.0479</v>
       </c>
       <c r="G7" t="n">
-        <v>0.829</v>
+        <v>0.9147</v>
       </c>
       <c r="H7" t="n">
-        <v>5.7099</v>
+        <v>5.1621</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9689</v>
+        <v>2.7875</v>
       </c>
       <c r="J7" t="n">
-        <v>0.829</v>
+        <v>0.9147</v>
       </c>
       <c r="K7" t="n">
         <v>144</v>
@@ -759,7 +759,7 @@
         <v>122</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7979</v>
+        <v>3.7022</v>
       </c>
       <c r="N7" t="n">
         <v>266</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.897</v>
+        <v>3.8797</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3961</v>
+        <v>1.3899</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1213</v>
+        <v>1.1419</v>
       </c>
       <c r="E8" t="n">
-        <v>3.897</v>
+        <v>3.8797</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1644</v>
+        <v>3.0954</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7326</v>
+        <v>0.7843</v>
       </c>
       <c r="H8" t="n">
-        <v>5.663</v>
+        <v>5.3188</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9445</v>
+        <v>2.8721</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7326</v>
+        <v>0.7843</v>
       </c>
       <c r="K8" t="n">
         <v>166</v>
@@ -805,7 +805,7 @@
         <v>54</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6771</v>
+        <v>3.6564</v>
       </c>
       <c r="N8" t="n">
         <v>220</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5082</v>
+        <v>3.5739</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2568</v>
+        <v>1.2804</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9458</v>
+        <v>1.0027</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5082</v>
+        <v>3.5739</v>
       </c>
       <c r="F9" t="n">
-        <v>2.533</v>
+        <v>2.4576</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9752</v>
+        <v>1.1163</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4386</v>
+        <v>3.2145</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7879</v>
+        <v>1.7358</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9752</v>
+        <v>1.1163</v>
       </c>
       <c r="K9" t="n">
         <v>44</v>
@@ -851,7 +851,7 @@
         <v>124</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7631</v>
+        <v>2.8521</v>
       </c>
       <c r="N9" t="n">
         <v>168</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4056</v>
+        <v>3.3444</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2201</v>
+        <v>1.1981</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8994</v>
+        <v>0.8982</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4056</v>
+        <v>3.3444</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6415</v>
+        <v>2.5264</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7641</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8207</v>
+        <v>3.4413</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9866</v>
+        <v>1.8583</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7641</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K10" t="n">
         <v>166</v>
@@ -897,7 +897,7 @@
         <v>54</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7507</v>
+        <v>2.6763</v>
       </c>
       <c r="N10" t="n">
         <v>220</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9498</v>
+        <v>2.9254</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0568</v>
+        <v>1.048</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6937</v>
+        <v>0.7075</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9498</v>
+        <v>2.9254</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9406</v>
+        <v>1.8456</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0092</v>
+        <v>1.0798</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9406</v>
+        <v>1.8456</v>
       </c>
       <c r="I11" t="n">
-        <v>1.009</v>
+        <v>0.9966</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0092</v>
+        <v>1.0798</v>
       </c>
       <c r="K11" t="n">
         <v>44</v>
@@ -943,7 +943,7 @@
         <v>124</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0182</v>
+        <v>2.0764</v>
       </c>
       <c r="N11" t="n">
         <v>168</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6913</v>
+        <v>2.5979</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.9307</v>
       </c>
       <c r="D12" t="n">
-        <v>0.577</v>
+        <v>0.5584</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6913</v>
+        <v>2.5979</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6468</v>
+        <v>2.5607</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0445</v>
+        <v>0.0372</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8394</v>
+        <v>3.5545</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9963</v>
+        <v>1.9194</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0445</v>
+        <v>0.0372</v>
       </c>
       <c r="K12" t="n">
         <v>166</v>
@@ -989,7 +989,7 @@
         <v>54</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0408</v>
+        <v>1.9566</v>
       </c>
       <c r="N12" t="n">
         <v>220</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6593</v>
+        <v>2.55</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9527</v>
+        <v>0.9135</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5625</v>
+        <v>0.5366</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6593</v>
+        <v>2.55</v>
       </c>
       <c r="F13" t="n">
-        <v>2.422</v>
+        <v>2.3164</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2373</v>
+        <v>0.2336</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0472</v>
+        <v>2.7484</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5844</v>
+        <v>1.4841</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2373</v>
+        <v>0.2336</v>
       </c>
       <c r="K13" t="n">
         <v>166</v>
@@ -1035,7 +1035,7 @@
         <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8217</v>
+        <v>1.7177</v>
       </c>
       <c r="N13" t="n">
         <v>220</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4804</v>
+        <v>2.3311</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.8351</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4818</v>
+        <v>0.437</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4804</v>
+        <v>2.3311</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4804</v>
+        <v>2.3311</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4804</v>
+        <v>2.3772</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4804</v>
+        <v>2.3772</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4804</v>
+        <v>2.3772</v>
       </c>
       <c r="N14" t="n">
         <v>111</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.416</v>
+        <v>2.3269</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8655</v>
+        <v>0.8336</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4527</v>
+        <v>0.435</v>
       </c>
       <c r="E15" t="n">
-        <v>2.416</v>
+        <v>2.3269</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3648</v>
+        <v>2.2963</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0512</v>
+        <v>0.0306</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8456</v>
+        <v>2.6823</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4796</v>
+        <v>1.4484</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0512</v>
+        <v>0.0306</v>
       </c>
       <c r="K15" t="n">
         <v>66</v>
@@ -1127,7 +1127,7 @@
         <v>52</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5308</v>
+        <v>1.479</v>
       </c>
       <c r="N15" t="n">
         <v>118</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0701</v>
+        <v>1.9854</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7416</v>
+        <v>0.7113</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2965</v>
+        <v>0.2796</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0701</v>
+        <v>1.9854</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0701</v>
+        <v>2.9854</v>
       </c>
       <c r="G16" t="n">
         <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>5.3309</v>
+        <v>4.9558</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7718</v>
+        <v>2.6761</v>
       </c>
       <c r="J16" t="n">
         <v>-1</v>
@@ -1173,7 +1173,7 @@
         <v>54</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7718</v>
+        <v>1.6761</v>
       </c>
       <c r="N16" t="n">
         <v>220</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8573</v>
+        <v>1.8832</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6654</v>
+        <v>0.6747</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2005</v>
+        <v>0.2331</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8573</v>
+        <v>1.8832</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8573</v>
+        <v>1.8832</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8573</v>
+        <v>1.8832</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8573</v>
+        <v>1.8832</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8573</v>
+        <v>1.8832</v>
       </c>
       <c r="N17" t="n">
         <v>111</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8431</v>
+        <v>1.7548</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6603</v>
+        <v>0.6287</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1941</v>
+        <v>0.1746</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8431</v>
+        <v>1.7548</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3815</v>
+        <v>2.317</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5384</v>
+        <v>-0.5622</v>
       </c>
       <c r="H18" t="n">
-        <v>2.9045</v>
+        <v>2.7506</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5102</v>
+        <v>1.4853</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5384</v>
+        <v>-0.5622</v>
       </c>
       <c r="K18" t="n">
         <v>66</v>
@@ -1265,7 +1265,7 @@
         <v>52</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9718</v>
+        <v>0.9231</v>
       </c>
       <c r="N18" t="n">
         <v>118</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2771</v>
+        <v>1.3769</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4575</v>
+        <v>0.4933</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0615</v>
+        <v>0.0026</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2771</v>
+        <v>1.3769</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5801</v>
+        <v>1.5241</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.303</v>
+        <v>-0.1472</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5801</v>
+        <v>1.5241</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8216</v>
+        <v>0.823</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.303</v>
+        <v>-0.1472</v>
       </c>
       <c r="K19" t="n">
         <v>44</v>
@@ -1311,7 +1311,7 @@
         <v>124</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.6758</v>
       </c>
       <c r="N19" t="n">
         <v>168</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2193</v>
+        <v>1.1879</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4368</v>
+        <v>0.4256</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0876</v>
+        <v>-0.0834</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2193</v>
+        <v>1.1879</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2193</v>
+        <v>1.1879</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2193</v>
+        <v>1.1879</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2193</v>
+        <v>1.1879</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2193</v>
+        <v>1.1879</v>
       </c>
       <c r="N20" t="n">
         <v>113</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0532</v>
+        <v>1.0422</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3773</v>
+        <v>0.3734</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1625</v>
+        <v>-0.1498</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0532</v>
+        <v>1.0422</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0532</v>
+        <v>1.0422</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0532</v>
+        <v>1.0422</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0532</v>
+        <v>1.0422</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0532</v>
+        <v>1.0422</v>
       </c>
       <c r="N21" t="n">
         <v>94</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8612</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3085</v>
+        <v>0.2985</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2492</v>
+        <v>-0.2449</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8612</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6333</v>
+        <v>0.6139</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2279</v>
+        <v>0.2193</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6333</v>
+        <v>0.6139</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3293</v>
+        <v>0.3315</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2279</v>
+        <v>0.2193</v>
       </c>
       <c r="K22" t="n">
         <v>66</v>
@@ -1449,7 +1449,7 @@
         <v>52</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5571999999999999</v>
+        <v>0.5508</v>
       </c>
       <c r="N22" t="n">
         <v>118</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7267</v>
+        <v>0.6596</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2603</v>
+        <v>0.2363</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3099</v>
+        <v>-0.3239</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7267</v>
+        <v>0.6596</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7267</v>
+        <v>0.6596</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7267</v>
+        <v>0.6596</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7267</v>
+        <v>0.6596</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7267</v>
+        <v>0.6596</v>
       </c>
       <c r="N23" t="n">
         <v>111</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6382</v>
+        <v>0.5745</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2286</v>
+        <v>0.2058</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3499</v>
+        <v>-0.3627</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6382</v>
+        <v>0.5745</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6382</v>
+        <v>0.5745</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6382</v>
+        <v>0.5745</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6382</v>
+        <v>0.5745</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6382</v>
+        <v>0.5745</v>
       </c>
       <c r="N24" t="n">
         <v>111</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4803</v>
+        <v>0.3644</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1721</v>
+        <v>0.1305</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4212</v>
+        <v>-0.4583</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4803</v>
+        <v>0.3644</v>
       </c>
       <c r="F25" t="n">
-        <v>0.927</v>
+        <v>0.8448</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4467</v>
+        <v>-0.4804</v>
       </c>
       <c r="H25" t="n">
-        <v>0.927</v>
+        <v>0.8448</v>
       </c>
       <c r="I25" t="n">
-        <v>0.482</v>
+        <v>0.4562</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4467</v>
+        <v>-0.4804</v>
       </c>
       <c r="K25" t="n">
         <v>66</v>
@@ -1587,7 +1587,7 @@
         <v>52</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0353</v>
+        <v>-0.0242</v>
       </c>
       <c r="N25" t="n">
         <v>118</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3313</v>
+        <v>0.2778</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1187</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4884</v>
+        <v>-0.4977</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3313</v>
+        <v>0.2778</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3313</v>
+        <v>0.2778</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3313</v>
+        <v>0.2778</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3313</v>
+        <v>0.2778</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3313</v>
+        <v>0.2778</v>
       </c>
       <c r="N26" t="n">
         <v>94</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3011</v>
+        <v>0.2566</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1079</v>
+        <v>0.0919</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5021</v>
+        <v>-0.5074</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3011</v>
+        <v>0.2566</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3011</v>
+        <v>0.2566</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3011</v>
+        <v>0.2566</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3011</v>
+        <v>0.2566</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3011</v>
+        <v>0.2566</v>
       </c>
       <c r="N27" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2729</v>
+        <v>0.231</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0978</v>
+        <v>0.0828</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5148</v>
+        <v>-0.519</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2729</v>
+        <v>0.231</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2729</v>
+        <v>0.231</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2729</v>
+        <v>0.231</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2729</v>
+        <v>0.231</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2729</v>
+        <v>0.231</v>
       </c>
       <c r="N28" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1629</v>
+        <v>0.1314</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0584</v>
+        <v>0.0471</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5645</v>
+        <v>-0.5644</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1629</v>
+        <v>0.1314</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1629</v>
+        <v>0.1314</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1629</v>
+        <v>0.1314</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1629</v>
+        <v>0.1314</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1629</v>
+        <v>0.1314</v>
       </c>
       <c r="N29" t="n">
         <v>94</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2244</v>
+        <v>-0.279</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0804</v>
+        <v>-0.1</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7393</v>
+        <v>-0.7512</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2244</v>
+        <v>-0.279</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2244</v>
+        <v>-0.279</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2244</v>
+        <v>-0.279</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2244</v>
+        <v>-0.279</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2244</v>
+        <v>-0.279</v>
       </c>
       <c r="N30" t="n">
         <v>111</v>
@@ -1826,78 +1826,78 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3652</v>
+        <v>-0.3656</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1308</v>
+        <v>-0.131</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8028999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3652</v>
+        <v>-0.3656</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3652</v>
+        <v>-0.2483</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.1173</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3652</v>
+        <v>-0.2483</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3652</v>
+        <v>-0.1341</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.1173</v>
       </c>
       <c r="K31" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3652</v>
+        <v>-0.2514</v>
       </c>
       <c r="N31" t="n">
-        <v>94</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Friis</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3837</v>
+        <v>-0.3863</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1375</v>
+        <v>-0.1384</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8112</v>
+        <v>-0.8001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3837</v>
+        <v>-0.3863</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3837</v>
+        <v>-0.3863</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3837</v>
+        <v>-0.3863</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3837</v>
+        <v>-0.3863</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3837</v>
+        <v>-0.3863</v>
       </c>
       <c r="N32" t="n">
         <v>94</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3994</v>
+        <v>-0.4247</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1431</v>
+        <v>-0.1521</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8183</v>
+        <v>-0.8175</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3994</v>
+        <v>-0.4247</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3994</v>
+        <v>-0.4247</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3994</v>
+        <v>-0.4247</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3994</v>
+        <v>-0.4247</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3994</v>
+        <v>-0.4247</v>
       </c>
       <c r="N33" t="n">
         <v>113</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Friis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4158</v>
+        <v>-0.4272</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.149</v>
+        <v>-0.153</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8257</v>
+        <v>-0.8187</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4158</v>
+        <v>-0.4272</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3148</v>
+        <v>-0.4272</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.101</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3148</v>
+        <v>-0.4272</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1637</v>
+        <v>-0.4272</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.101</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="L34" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2647</v>
+        <v>-0.4272</v>
       </c>
       <c r="N34" t="n">
-        <v>118</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6087</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2181</v>
+        <v>-0.232</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-0.919</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6087</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6087</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6087</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6087</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6087</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>94</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.7821</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2786</v>
+        <v>-0.2802</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9891</v>
+        <v>-0.9802</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.7821</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.7821</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.7821</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.7821</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.7821</v>
       </c>
       <c r="N36" t="n">
         <v>113</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7865</v>
+        <v>-0.8065</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2818</v>
+        <v>-0.2889</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9931</v>
+        <v>-0.9913</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7865</v>
+        <v>-0.8065</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7865</v>
+        <v>-0.8065</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7865</v>
+        <v>-0.8065</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7865</v>
+        <v>-0.8065</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7865</v>
+        <v>-0.8065</v>
       </c>
       <c r="N37" t="n">
         <v>94</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8321</v>
+        <v>-0.8629</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2981</v>
+        <v>-0.3091</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0137</v>
+        <v>-1.017</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8321</v>
+        <v>-0.8629</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8321</v>
+        <v>-0.8629</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8321</v>
+        <v>-0.8629</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8321</v>
+        <v>-0.8629</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8321</v>
+        <v>-0.8629</v>
       </c>
       <c r="N38" t="n">
         <v>94</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9526</v>
+        <v>-0.9911</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3413</v>
+        <v>-0.3551</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0681</v>
+        <v>-1.0754</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9526</v>
+        <v>-0.9911</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9526</v>
+        <v>-0.9911</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9526</v>
+        <v>-0.9911</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9526</v>
+        <v>-0.9911</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9526</v>
+        <v>-0.9911</v>
       </c>
       <c r="N39" t="n">
         <v>113</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1948</v>
+        <v>-1.224</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.428</v>
+        <v>-0.4385</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1774</v>
+        <v>-1.1814</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1948</v>
+        <v>-1.224</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.1948</v>
+        <v>-1.224</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.1948</v>
+        <v>-1.224</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1948</v>
+        <v>-1.224</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.1948</v>
+        <v>-1.224</v>
       </c>
       <c r="N40" t="n">
         <v>94</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.6149</v>
+        <v>-3.193</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.295</v>
+        <v>-1.1439</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.27</v>
+        <v>-2.0777</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.6149</v>
+        <v>-3.193</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.6945</v>
+        <v>-2.3128</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.9204</v>
+        <v>-0.8802</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.6945</v>
+        <v>-2.3128</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.401</v>
+        <v>-1.2489</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9204</v>
+        <v>-0.8802</v>
       </c>
       <c r="K41" t="n">
         <v>144</v>
@@ -2323,7 +2323,7 @@
         <v>122</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.3214</v>
+        <v>-2.1291</v>
       </c>
       <c r="N41" t="n">
         <v>266</v>
@@ -2429,10 +2429,10 @@
         <v>1.14</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3511</v>
+        <v>0.3466</v>
       </c>
       <c r="J2" t="n">
-        <v>12.2885</v>
+        <v>12.131</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.92</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1042</v>
+        <v>-0.1179</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.647</v>
+        <v>-4.1265</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.89</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1368</v>
+        <v>-0.1517</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.788</v>
+        <v>-5.3095</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.86</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1685</v>
+        <v>-0.1839</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.8975</v>
+        <v>-6.4365</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.8</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2296</v>
+        <v>-0.2451</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.036</v>
+        <v>-8.5785</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.41</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0417</v>
+        <v>0.9909</v>
       </c>
       <c r="J7" t="n">
-        <v>36.4595</v>
+        <v>34.6815</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.576</v>
+        <v>0.556</v>
       </c>
       <c r="J8" t="n">
-        <v>20.16</v>
+        <v>19.46</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.17</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5009</v>
+        <v>0.4885</v>
       </c>
       <c r="J9" t="n">
-        <v>17.5315</v>
+        <v>17.0975</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1973</v>
+        <v>-0.1916</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.9055</v>
+        <v>-6.706</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4409</v>
+        <v>-0.4185</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.4315</v>
+        <v>-14.6475</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.13</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2991</v>
+        <v>0.3044</v>
       </c>
       <c r="J12" t="n">
-        <v>10.4685</v>
+        <v>10.654</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2399</v>
+        <v>0.2478</v>
       </c>
       <c r="J13" t="n">
-        <v>8.3965</v>
+        <v>8.673</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.06</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1564</v>
+        <v>0.1663</v>
       </c>
       <c r="J14" t="n">
-        <v>5.474</v>
+        <v>5.8205</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.01</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0346</v>
+        <v>0.0412</v>
       </c>
       <c r="J15" t="n">
-        <v>1.211</v>
+        <v>1.442</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.84</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2016</v>
+        <v>-0.2144</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.056</v>
+        <v>-7.504</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.46</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1213</v>
+        <v>1.1022</v>
       </c>
       <c r="J17" t="n">
-        <v>39.2455</v>
+        <v>38.577</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.09</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2979</v>
+        <v>0.3001</v>
       </c>
       <c r="J18" t="n">
-        <v>10.4265</v>
+        <v>10.5035</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.99</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0735</v>
+        <v>-0.0725</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.5725</v>
+        <v>-2.5375</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.98</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1145</v>
+        <v>-0.1138</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.0075</v>
+        <v>-3.983</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.9</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3728</v>
+        <v>-0.3586</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.048</v>
+        <v>-12.551</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.31</v>
       </c>
       <c r="I22" t="n">
-        <v>0.638</v>
+        <v>0.7033</v>
       </c>
       <c r="J22" t="n">
-        <v>18.502</v>
+        <v>20.3957</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4205</v>
+        <v>0.4608</v>
       </c>
       <c r="J23" t="n">
-        <v>12.1945</v>
+        <v>13.3632</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4205</v>
+        <v>0.4608</v>
       </c>
       <c r="J24" t="n">
-        <v>12.1945</v>
+        <v>13.3632</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.07</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2378</v>
+        <v>0.2445</v>
       </c>
       <c r="J25" t="n">
-        <v>6.8962</v>
+        <v>7.0905</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6243</v>
+        <v>-0.5847</v>
       </c>
       <c r="J26" t="n">
-        <v>-18.1047</v>
+        <v>-16.9563</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.3</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4814</v>
+        <v>0.5381</v>
       </c>
       <c r="J27" t="n">
-        <v>13.9606</v>
+        <v>15.6049</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.2</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3799</v>
+        <v>0.4136</v>
       </c>
       <c r="J28" t="n">
-        <v>11.0171</v>
+        <v>11.9944</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.13</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2847</v>
+        <v>0.294</v>
       </c>
       <c r="J29" t="n">
-        <v>8.2563</v>
+        <v>8.526</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.12</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2659</v>
+        <v>0.276</v>
       </c>
       <c r="J30" t="n">
-        <v>7.7111</v>
+        <v>8.004</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2991</v>
+        <v>-0.3094</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.6739</v>
+        <v>-8.9726</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.52</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8767</v>
+        <v>0.9698</v>
       </c>
       <c r="J32" t="n">
-        <v>21.9175</v>
+        <v>24.245</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.31</v>
       </c>
       <c r="I33" t="n">
-        <v>0.608</v>
+        <v>0.6771</v>
       </c>
       <c r="J33" t="n">
-        <v>15.2</v>
+        <v>16.9275</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.27</v>
       </c>
       <c r="I34" t="n">
-        <v>0.556</v>
+        <v>0.6191</v>
       </c>
       <c r="J34" t="n">
-        <v>13.9</v>
+        <v>15.4775</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.15</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3855</v>
+        <v>0.4216</v>
       </c>
       <c r="J35" t="n">
-        <v>9.637499999999999</v>
+        <v>10.54</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.11</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3131</v>
+        <v>0.3244</v>
       </c>
       <c r="J36" t="n">
-        <v>7.8275</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.16</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3842</v>
+        <v>0.4044</v>
       </c>
       <c r="J37" t="n">
-        <v>9.605</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.08</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2512</v>
+        <v>0.2462</v>
       </c>
       <c r="J38" t="n">
-        <v>6.28</v>
+        <v>6.155</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.96</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0474</v>
+        <v>-0.0604</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.185</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.8</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2214</v>
+        <v>-0.2388</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.535</v>
+        <v>-5.97</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.28</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7018</v>
+        <v>-0.6952</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.545</v>
+        <v>-17.38</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.14</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3621</v>
+        <v>0.369</v>
       </c>
       <c r="J42" t="n">
-        <v>8.6904</v>
+        <v>8.856</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.93</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.028</v>
+        <v>-2.3904</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.82</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.201</v>
+        <v>-0.2186</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.824</v>
+        <v>-5.2464</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.75</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2695</v>
+        <v>-0.2863</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.468</v>
+        <v>-6.8712</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.61</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4023</v>
+        <v>-0.4145</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.655200000000001</v>
+        <v>-9.948</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.77</v>
       </c>
       <c r="I47" t="n">
-        <v>1.2054</v>
+        <v>1.315</v>
       </c>
       <c r="J47" t="n">
-        <v>28.9296</v>
+        <v>31.56</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.31</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6186</v>
+        <v>0.6863</v>
       </c>
       <c r="J48" t="n">
-        <v>14.8464</v>
+        <v>16.4712</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.06</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1846</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
-        <v>4.4304</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0481</v>
+        <v>-0.0332</v>
       </c>
       <c r="J50" t="n">
-        <v>-1.1544</v>
+        <v>-0.7968</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.85</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5427</v>
+        <v>-0.5069</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.0248</v>
+        <v>-12.1656</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3207</v>
+        <v>0.3169</v>
       </c>
       <c r="J52" t="n">
-        <v>8.9796</v>
+        <v>8.873200000000001</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.11</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3013</v>
+        <v>0.2972</v>
       </c>
       <c r="J53" t="n">
-        <v>8.436400000000001</v>
+        <v>8.3216</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1342</v>
+        <v>-0.1497</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.7576</v>
+        <v>-4.1916</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.78</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2457</v>
+        <v>-0.2618</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.8796</v>
+        <v>-7.3304</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4539</v>
+        <v>-0.4626</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.7092</v>
+        <v>-12.9528</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.38</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7176</v>
+        <v>0.7935</v>
       </c>
       <c r="J57" t="n">
-        <v>20.0928</v>
+        <v>22.218</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.23</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5123</v>
+        <v>0.5674</v>
       </c>
       <c r="J58" t="n">
-        <v>14.3444</v>
+        <v>15.8872</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.22</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4982</v>
+        <v>0.5516</v>
       </c>
       <c r="J59" t="n">
-        <v>13.9496</v>
+        <v>15.4448</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.09</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2806</v>
+        <v>0.2884</v>
       </c>
       <c r="J60" t="n">
-        <v>7.8568</v>
+        <v>8.075200000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2755</v>
+        <v>-0.2628</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.714</v>
+        <v>-7.3584</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.75</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2394</v>
+        <v>-0.2631</v>
       </c>
       <c r="J62" t="n">
-        <v>-4.788</v>
+        <v>-5.262</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2991</v>
+        <v>-0.3207</v>
       </c>
       <c r="J63" t="n">
-        <v>-5.982</v>
+        <v>-6.414</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.68</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3086</v>
+        <v>-0.3299</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.172</v>
+        <v>-6.598</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.63</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3531</v>
+        <v>-0.3729</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.062</v>
+        <v>-7.458</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.48</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4924</v>
+        <v>-0.5044</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.848000000000001</v>
+        <v>-10.088</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.63</v>
       </c>
       <c r="I67" t="n">
-        <v>1.2418</v>
+        <v>1.2232</v>
       </c>
       <c r="J67" t="n">
-        <v>24.836</v>
+        <v>24.464</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.53</v>
       </c>
       <c r="I68" t="n">
-        <v>1.127</v>
+        <v>1.0991</v>
       </c>
       <c r="J68" t="n">
-        <v>22.54</v>
+        <v>21.982</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.49</v>
       </c>
       <c r="I69" t="n">
-        <v>1.0812</v>
+        <v>1.0481</v>
       </c>
       <c r="J69" t="n">
-        <v>21.624</v>
+        <v>20.962</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.48</v>
       </c>
       <c r="I70" t="n">
-        <v>1.0694</v>
+        <v>1.0343</v>
       </c>
       <c r="J70" t="n">
-        <v>21.388</v>
+        <v>20.686</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.47</v>
       </c>
       <c r="I71" t="n">
-        <v>1.0573</v>
+        <v>1.0199</v>
       </c>
       <c r="J71" t="n">
-        <v>21.146</v>
+        <v>20.398</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.48</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8869</v>
+        <v>0.8447</v>
       </c>
       <c r="J72" t="n">
-        <v>25.7201</v>
+        <v>24.4963</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7739</v>
+        <v>0.7436</v>
       </c>
       <c r="J73" t="n">
-        <v>22.4431</v>
+        <v>21.5644</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.96</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0709</v>
+        <v>-0.0785</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.0561</v>
+        <v>-2.2765</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1753</v>
+        <v>-0.1868</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.0837</v>
+        <v>-5.4172</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.66</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3817</v>
+        <v>-0.3902</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.0693</v>
+        <v>-11.3158</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.3</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8187</v>
+        <v>0.7704</v>
       </c>
       <c r="J77" t="n">
-        <v>23.7423</v>
+        <v>22.3416</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.2</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5766</v>
+        <v>0.5564</v>
       </c>
       <c r="J78" t="n">
-        <v>16.7214</v>
+        <v>16.1356</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.19</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5517</v>
+        <v>0.5341</v>
       </c>
       <c r="J79" t="n">
-        <v>15.9993</v>
+        <v>15.4889</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.07</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2335</v>
+        <v>0.2415</v>
       </c>
       <c r="J80" t="n">
-        <v>6.7715</v>
+        <v>7.0035</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.85</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5232</v>
+        <v>-0.4932</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.1728</v>
+        <v>-14.3028</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0577</v>
+        <v>0.0419</v>
       </c>
       <c r="J82" t="n">
-        <v>1.3271</v>
+        <v>0.9637</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.99</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0175</v>
+        <v>-0.0019</v>
       </c>
       <c r="J83" t="n">
-        <v>0.4025</v>
+        <v>-0.0437</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.85</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1657</v>
+        <v>-0.1844</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.8111</v>
+        <v>-4.2412</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.68</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3292</v>
+        <v>-0.3457</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.5716</v>
+        <v>-7.9511</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.47</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5312</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.0681</v>
+        <v>-12.2176</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.5</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1208</v>
+        <v>1.086</v>
       </c>
       <c r="J87" t="n">
-        <v>25.7784</v>
+        <v>24.978</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.43</v>
       </c>
       <c r="I88" t="n">
-        <v>1.0306</v>
+        <v>0.982</v>
       </c>
       <c r="J88" t="n">
-        <v>23.7038</v>
+        <v>22.586</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.38</v>
       </c>
       <c r="I89" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.8924</v>
       </c>
       <c r="J89" t="n">
-        <v>21.7373</v>
+        <v>20.5252</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.19</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5177</v>
+        <v>0.5109</v>
       </c>
       <c r="J90" t="n">
-        <v>11.9071</v>
+        <v>11.7507</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.98</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.168</v>
+        <v>-0.1512</v>
       </c>
       <c r="J91" t="n">
-        <v>-3.864</v>
+        <v>-3.4776</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.92</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.0519</v>
+        <v>-0.0771</v>
       </c>
       <c r="J92" t="n">
-        <v>-1.0899</v>
+        <v>-1.6191</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.73</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2641</v>
+        <v>-0.2862</v>
       </c>
       <c r="J93" t="n">
-        <v>-5.5461</v>
+        <v>-6.0102</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.7</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2931</v>
+        <v>-0.3142</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.1551</v>
+        <v>-6.5982</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.6</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3836</v>
+        <v>-0.4014</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.0556</v>
+        <v>-8.429399999999999</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.38</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5899</v>
+        <v>-0.5945</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.3879</v>
+        <v>-12.4845</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>1.6734</v>
+        <v>1.6774</v>
       </c>
       <c r="J97" t="n">
-        <v>35.1414</v>
+        <v>35.2254</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.99</v>
       </c>
       <c r="I98" t="n">
-        <v>1.6622</v>
+        <v>1.6657</v>
       </c>
       <c r="J98" t="n">
-        <v>34.9062</v>
+        <v>34.9797</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.45</v>
       </c>
       <c r="I99" t="n">
-        <v>1.0375</v>
+        <v>0.9951</v>
       </c>
       <c r="J99" t="n">
-        <v>21.7875</v>
+        <v>20.8971</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.19</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4833</v>
+        <v>0.487</v>
       </c>
       <c r="J100" t="n">
-        <v>10.1493</v>
+        <v>10.227</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.65</v>
       </c>
       <c r="I101" t="n">
-        <v>-1.0893</v>
+        <v>-0.9809</v>
       </c>
       <c r="J101" t="n">
-        <v>-22.8753</v>
+        <v>-20.5989</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.42</v>
       </c>
       <c r="I102" t="n">
-        <v>0.536</v>
+        <v>0.543</v>
       </c>
       <c r="J102" t="n">
-        <v>14.472</v>
+        <v>14.661</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.28</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3764</v>
+        <v>0.3912</v>
       </c>
       <c r="J103" t="n">
-        <v>10.1628</v>
+        <v>10.5624</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.22</v>
       </c>
       <c r="I104" t="n">
-        <v>0.3056</v>
+        <v>0.3226</v>
       </c>
       <c r="J104" t="n">
-        <v>8.251200000000001</v>
+        <v>8.7102</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.06</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0931</v>
+        <v>0.1099</v>
       </c>
       <c r="J105" t="n">
-        <v>2.5137</v>
+        <v>2.9673</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.0183</v>
+        <v>-0.0141</v>
       </c>
       <c r="J106" t="n">
-        <v>-0.4941</v>
+        <v>-0.3807</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.11</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2194</v>
+        <v>0.2245</v>
       </c>
       <c r="J107" t="n">
-        <v>5.9238</v>
+        <v>6.0615</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.08</v>
       </c>
       <c r="I108" t="n">
-        <v>0.171</v>
+        <v>0.1769</v>
       </c>
       <c r="J108" t="n">
-        <v>4.617</v>
+        <v>4.7763</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.98</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0303</v>
+        <v>-0.0384</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.8181</v>
+        <v>-1.0368</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2801</v>
+        <v>-0.2945</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.5627</v>
+        <v>-7.9515</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.74</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2898</v>
+        <v>-0.304</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.8246</v>
+        <v>-8.208</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.06</v>
       </c>
       <c r="I112" t="n">
-        <v>0.204</v>
+        <v>0.2009</v>
       </c>
       <c r="J112" t="n">
-        <v>4.692</v>
+        <v>4.6207</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0738</v>
+        <v>-0.0881</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.6974</v>
+        <v>-2.0263</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.91</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1093</v>
+        <v>-0.1249</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.5139</v>
+        <v>-2.8727</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.71</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3093</v>
+        <v>-0.3248</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.1139</v>
+        <v>-7.4704</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.68</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3379</v>
+        <v>-0.3524</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.7717</v>
+        <v>-8.1052</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.45</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0597</v>
+        <v>1.0159</v>
       </c>
       <c r="J117" t="n">
-        <v>24.3731</v>
+        <v>23.3657</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.39</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9665</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="J118" t="n">
-        <v>22.2295</v>
+        <v>20.9944</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.24</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6402</v>
+        <v>0.6202</v>
       </c>
       <c r="J119" t="n">
-        <v>14.7246</v>
+        <v>14.2646</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.21</v>
       </c>
       <c r="I120" t="n">
-        <v>0.5689</v>
+        <v>0.5564</v>
       </c>
       <c r="J120" t="n">
-        <v>13.0847</v>
+        <v>12.7972</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.14</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3918</v>
+        <v>0.3966</v>
       </c>
       <c r="J121" t="n">
-        <v>9.0114</v>
+        <v>9.1218</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.11</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2641</v>
+        <v>0.2701</v>
       </c>
       <c r="J122" t="n">
-        <v>11.0922</v>
+        <v>11.3442</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.11</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2641</v>
+        <v>0.2701</v>
       </c>
       <c r="J123" t="n">
-        <v>11.0922</v>
+        <v>11.3442</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.98</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0368</v>
+        <v>-0.0434</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.5456</v>
+        <v>-1.8228</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.96</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.0733</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.6964</v>
+        <v>-3.0786</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.89</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.1464</v>
+        <v>-0.1591</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.1488</v>
+        <v>-6.6822</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.52</v>
       </c>
       <c r="I127" t="n">
-        <v>1.1743</v>
+        <v>1.1381</v>
       </c>
       <c r="J127" t="n">
-        <v>49.3206</v>
+        <v>47.8002</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.4</v>
       </c>
       <c r="I128" t="n">
-        <v>1.0128</v>
+        <v>0.9556</v>
       </c>
       <c r="J128" t="n">
-        <v>42.5376</v>
+        <v>40.1352</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.08</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2515</v>
+        <v>0.2613</v>
       </c>
       <c r="J129" t="n">
-        <v>10.563</v>
+        <v>10.9746</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.02</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0544</v>
+        <v>0.0725</v>
       </c>
       <c r="J130" t="n">
-        <v>2.2848</v>
+        <v>3.045</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.84</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5631</v>
+        <v>-0.5266</v>
       </c>
       <c r="J131" t="n">
-        <v>-23.6502</v>
+        <v>-22.1172</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.39</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9868</v>
+        <v>0.9294</v>
       </c>
       <c r="J132" t="n">
-        <v>22.6964</v>
+        <v>21.3762</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.34</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8837</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="J133" t="n">
-        <v>20.3251</v>
+        <v>19.1406</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.26</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6999</v>
+        <v>0.6705</v>
       </c>
       <c r="J134" t="n">
-        <v>16.0977</v>
+        <v>15.4215</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.1</v>
       </c>
       <c r="I135" t="n">
-        <v>0.3016</v>
+        <v>0.3096</v>
       </c>
       <c r="J135" t="n">
-        <v>6.9368</v>
+        <v>7.1208</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.93</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3149</v>
+        <v>-0.2978</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.2427</v>
+        <v>-6.8494</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.04</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1573</v>
+        <v>0.1546</v>
       </c>
       <c r="J137" t="n">
-        <v>3.6179</v>
+        <v>3.5558</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.95</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0606</v>
+        <v>-0.0743</v>
       </c>
       <c r="J138" t="n">
-        <v>-1.3938</v>
+        <v>-1.7089</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.89</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1309</v>
+        <v>-0.1473</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.0107</v>
+        <v>-3.3879</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.73</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2896</v>
+        <v>-0.3057</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.6608</v>
+        <v>-7.0311</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.67</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3468</v>
+        <v>-0.3611</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.9764</v>
+        <v>-8.305300000000001</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.14</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2752</v>
+        <v>0.2764</v>
       </c>
       <c r="J142" t="n">
-        <v>7.1552</v>
+        <v>7.1864</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0159</v>
+        <v>0.0117</v>
       </c>
       <c r="J143" t="n">
-        <v>0.4134</v>
+        <v>0.3042</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.0592</v>
+        <v>-2.3998</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.84</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1866</v>
+        <v>-0.2028</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.8516</v>
+        <v>-5.2728</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.58</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4364</v>
+        <v>-0.4459</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.3464</v>
+        <v>-11.5934</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.42</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5407</v>
+        <v>0.5465</v>
       </c>
       <c r="J147" t="n">
-        <v>14.0582</v>
+        <v>14.209</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.16</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2352</v>
+        <v>0.2525</v>
       </c>
       <c r="J148" t="n">
-        <v>6.1152</v>
+        <v>6.565</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.13</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1965</v>
+        <v>0.2139</v>
       </c>
       <c r="J149" t="n">
-        <v>5.109</v>
+        <v>5.5614</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.09</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1411</v>
+        <v>0.1582</v>
       </c>
       <c r="J150" t="n">
-        <v>3.6686</v>
+        <v>4.1132</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.06</v>
       </c>
       <c r="I151" t="n">
-        <v>0.096</v>
+        <v>0.1122</v>
       </c>
       <c r="J151" t="n">
-        <v>2.496</v>
+        <v>2.9172</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.42</v>
       </c>
       <c r="I152" t="n">
-        <v>1.025</v>
+        <v>0.9735</v>
       </c>
       <c r="J152" t="n">
-        <v>26.65</v>
+        <v>25.311</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.42</v>
       </c>
       <c r="I153" t="n">
-        <v>1.025</v>
+        <v>0.9735</v>
       </c>
       <c r="J153" t="n">
-        <v>26.65</v>
+        <v>25.311</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.39</v>
       </c>
       <c r="I154" t="n">
-        <v>0.9749</v>
+        <v>0.9195</v>
       </c>
       <c r="J154" t="n">
-        <v>25.3474</v>
+        <v>23.907</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.24</v>
       </c>
       <c r="I155" t="n">
-        <v>0.6463</v>
+        <v>0.6243</v>
       </c>
       <c r="J155" t="n">
-        <v>16.8038</v>
+        <v>16.2318</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.78</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7377</v>
+        <v>-0.6788</v>
       </c>
       <c r="J156" t="n">
-        <v>-19.1802</v>
+        <v>-17.6488</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.02</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1303</v>
+        <v>0.1202</v>
       </c>
       <c r="J157" t="n">
-        <v>3.3878</v>
+        <v>3.1252</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.85</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1651</v>
+        <v>-0.1839</v>
       </c>
       <c r="J158" t="n">
-        <v>-4.2926</v>
+        <v>-4.7814</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.84</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1755</v>
+        <v>-0.1944</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.563</v>
+        <v>-5.0544</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.73</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2812</v>
+        <v>-0.2992</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.3112</v>
+        <v>-7.7792</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.53</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4689</v>
+        <v>-0.4789</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.1914</v>
+        <v>-12.4514</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.33</v>
       </c>
       <c r="I162" t="n">
-        <v>0.643</v>
+        <v>0.6253</v>
       </c>
       <c r="J162" t="n">
-        <v>26.363</v>
+        <v>25.6373</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.32</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6262</v>
+        <v>0.61</v>
       </c>
       <c r="J163" t="n">
-        <v>25.6742</v>
+        <v>25.01</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.03</v>
       </c>
       <c r="I164" t="n">
-        <v>0.082</v>
+        <v>0.0931</v>
       </c>
       <c r="J164" t="n">
-        <v>3.362</v>
+        <v>3.8171</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.85</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.196</v>
+        <v>-0.2078</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.036</v>
+        <v>-8.5198</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2167</v>
+        <v>-0.2285</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.8847</v>
+        <v>-9.368499999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.08</v>
       </c>
       <c r="I167" t="n">
-        <v>0.2908</v>
+        <v>0.2881</v>
       </c>
       <c r="J167" t="n">
-        <v>11.9228</v>
+        <v>11.8121</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.07</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2606</v>
+        <v>0.2599</v>
       </c>
       <c r="J168" t="n">
-        <v>10.6846</v>
+        <v>10.6559</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.99</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.053</v>
+        <v>-0.0585</v>
       </c>
       <c r="J169" t="n">
-        <v>-2.173</v>
+        <v>-2.3985</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.95</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1967</v>
+        <v>-0.1999</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.0647</v>
+        <v>-8.1959</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.9</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3483</v>
+        <v>-0.3416</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.2803</v>
+        <v>-14.0056</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.41</v>
       </c>
       <c r="I172" t="n">
-        <v>1.0122</v>
+        <v>0.9585</v>
       </c>
       <c r="J172" t="n">
-        <v>25.305</v>
+        <v>23.9625</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.27</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7157</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="J173" t="n">
-        <v>17.8925</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.24</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6476</v>
+        <v>0.6252</v>
       </c>
       <c r="J174" t="n">
-        <v>16.19</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.16</v>
       </c>
       <c r="I175" t="n">
-        <v>0.4547</v>
+        <v>0.4514</v>
       </c>
       <c r="J175" t="n">
-        <v>11.3675</v>
+        <v>11.285</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.11</v>
       </c>
       <c r="I176" t="n">
-        <v>0.3216</v>
+        <v>0.3299</v>
       </c>
       <c r="J176" t="n">
-        <v>8.039999999999999</v>
+        <v>8.2475</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.13</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3629</v>
+        <v>0.3512</v>
       </c>
       <c r="J177" t="n">
-        <v>9.0725</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.96</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0457</v>
+        <v>-0.0591</v>
       </c>
       <c r="J178" t="n">
-        <v>-1.1425</v>
+        <v>-1.4775</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.79</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.23</v>
+        <v>-0.2475</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.75</v>
+        <v>-6.1875</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.74</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2786</v>
+        <v>-0.2953</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.965</v>
+        <v>-7.3825</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.61</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4018</v>
+        <v>-0.4141</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.045</v>
+        <v>-10.3525</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.61</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2496</v>
+        <v>1.2254</v>
       </c>
       <c r="J182" t="n">
-        <v>31.24</v>
+        <v>30.635</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.56</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1888</v>
+        <v>1.1603</v>
       </c>
       <c r="J183" t="n">
-        <v>29.72</v>
+        <v>29.0075</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.26</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6787</v>
+        <v>0.6561</v>
       </c>
       <c r="J184" t="n">
-        <v>16.9675</v>
+        <v>16.4025</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.14</v>
       </c>
       <c r="I185" t="n">
-        <v>0.3823</v>
+        <v>0.39</v>
       </c>
       <c r="J185" t="n">
-        <v>9.557499999999999</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.07</v>
       </c>
       <c r="I186" t="n">
-        <v>0.1846</v>
+        <v>0.2075</v>
       </c>
       <c r="J186" t="n">
-        <v>4.615</v>
+        <v>5.1875</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.88</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1223</v>
+        <v>-0.1432</v>
       </c>
       <c r="J187" t="n">
-        <v>-3.0575</v>
+        <v>-3.58</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.85</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1557</v>
+        <v>-0.1767</v>
       </c>
       <c r="J188" t="n">
-        <v>-3.8925</v>
+        <v>-4.4175</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.73</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2746</v>
+        <v>-0.2942</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.865</v>
+        <v>-7.355</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.68</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.321</v>
+        <v>-0.3393</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.025</v>
+        <v>-8.4825</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.57</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.424</v>
+        <v>-0.4377</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.6</v>
+        <v>-10.9425</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.01</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2152</v>
+        <v>0.1739</v>
       </c>
       <c r="J192" t="n">
-        <v>4.5192</v>
+        <v>3.6519</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2938</v>
+        <v>-0.3166</v>
       </c>
       <c r="J193" t="n">
-        <v>-6.1698</v>
+        <v>-6.6486</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.62</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3589</v>
+        <v>-0.3791</v>
       </c>
       <c r="J194" t="n">
-        <v>-7.5369</v>
+        <v>-7.9611</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.52</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.45</v>
+        <v>-0.4655</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.775499999999999</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.26</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6973</v>
+        <v>-0.6938</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.6433</v>
+        <v>-14.5698</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>2.04</v>
       </c>
       <c r="I197" t="n">
-        <v>1.7014</v>
+        <v>1.7093</v>
       </c>
       <c r="J197" t="n">
-        <v>35.7294</v>
+        <v>35.8953</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.6</v>
       </c>
       <c r="I198" t="n">
-        <v>1.2067</v>
+        <v>1.1856</v>
       </c>
       <c r="J198" t="n">
-        <v>25.3407</v>
+        <v>24.8976</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.45</v>
       </c>
       <c r="I199" t="n">
-        <v>1.0306</v>
+        <v>0.9889</v>
       </c>
       <c r="J199" t="n">
-        <v>21.6426</v>
+        <v>20.7669</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.27</v>
       </c>
       <c r="I200" t="n">
-        <v>0.6619</v>
+        <v>0.6489</v>
       </c>
       <c r="J200" t="n">
-        <v>13.8999</v>
+        <v>13.6269</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.27</v>
       </c>
       <c r="I201" t="n">
-        <v>0.6619</v>
+        <v>0.6489</v>
       </c>
       <c r="J201" t="n">
-        <v>13.8999</v>
+        <v>13.6269</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.13</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3698</v>
+        <v>0.3562</v>
       </c>
       <c r="J202" t="n">
-        <v>9.244999999999999</v>
+        <v>8.904999999999999</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.92</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0935</v>
+        <v>-0.1097</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.3375</v>
+        <v>-2.7425</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.76</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2574</v>
+        <v>-0.2749</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.435</v>
+        <v>-6.8725</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.75</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2671</v>
+        <v>-0.2844</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.6775</v>
+        <v>-7.11</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.6</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4092</v>
+        <v>-0.4214</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.23</v>
+        <v>-10.535</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.94</v>
       </c>
       <c r="I207" t="n">
-        <v>1.6536</v>
+        <v>1.6492</v>
       </c>
       <c r="J207" t="n">
-        <v>41.34</v>
+        <v>41.23</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.22</v>
       </c>
       <c r="I208" t="n">
-        <v>0.5934</v>
+        <v>0.5782</v>
       </c>
       <c r="J208" t="n">
-        <v>14.835</v>
+        <v>14.455</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.2</v>
       </c>
       <c r="I209" t="n">
-        <v>0.545</v>
+        <v>0.5349</v>
       </c>
       <c r="J209" t="n">
-        <v>13.625</v>
+        <v>13.3725</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.13</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3656</v>
+        <v>0.3726</v>
       </c>
       <c r="J210" t="n">
-        <v>9.140000000000001</v>
+        <v>9.315</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.93</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3342</v>
+        <v>-0.3113</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.355</v>
+        <v>-7.7825</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.65</v>
       </c>
       <c r="I212" t="n">
-        <v>1.2835</v>
+        <v>1.2642</v>
       </c>
       <c r="J212" t="n">
-        <v>24.3865</v>
+        <v>24.0198</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.53</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1403</v>
+        <v>1.1106</v>
       </c>
       <c r="J213" t="n">
-        <v>21.6657</v>
+        <v>21.1014</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.5</v>
       </c>
       <c r="I214" t="n">
-        <v>1.1041</v>
+        <v>1.0713</v>
       </c>
       <c r="J214" t="n">
-        <v>20.9779</v>
+        <v>20.3547</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.27</v>
       </c>
       <c r="I215" t="n">
-        <v>0.6874</v>
+        <v>0.6667</v>
       </c>
       <c r="J215" t="n">
-        <v>13.0606</v>
+        <v>12.6673</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.05</v>
       </c>
       <c r="I216" t="n">
-        <v>0.1059</v>
+        <v>0.137</v>
       </c>
       <c r="J216" t="n">
-        <v>2.0121</v>
+        <v>2.603</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.88</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.1033</v>
+        <v>-0.1284</v>
       </c>
       <c r="J217" t="n">
-        <v>-1.9627</v>
+        <v>-2.4396</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.84</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.1496</v>
+        <v>-0.1742</v>
       </c>
       <c r="J218" t="n">
-        <v>-2.8424</v>
+        <v>-3.3098</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.71</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2847</v>
+        <v>-0.3058</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.4093</v>
+        <v>-5.8102</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.57</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4125</v>
+        <v>-0.4287</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.8375</v>
+        <v>-8.145300000000001</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.36</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6096</v>
+        <v>-0.6125</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.5824</v>
+        <v>-11.6375</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1977/event_1977_evp_summary.xlsx
+++ b/database/event/1977/event_1977_evp_summary.xlsx
@@ -492,93 +492,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.1102</v>
+        <v>5.1155</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8307</v>
+        <v>1.8326</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7021</v>
+        <v>1.7246</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1102</v>
+        <v>5.1155</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6334</v>
+        <v>2.5228</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4768</v>
+        <v>2.5927</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7945</v>
+        <v>3.0292</v>
       </c>
       <c r="I2" t="n">
-        <v>2.049</v>
+        <v>1.7008</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4768</v>
+        <v>2.5927</v>
       </c>
       <c r="K2" t="n">
-        <v>144</v>
+        <v>44</v>
       </c>
       <c r="L2" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M2" t="n">
-        <v>4.5258</v>
+        <v>4.2935</v>
       </c>
       <c r="N2" t="n">
-        <v>266</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.1083</v>
+        <v>5.0301</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8301</v>
+        <v>1.802</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7012</v>
+        <v>1.6857</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1083</v>
+        <v>5.0301</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4463</v>
+        <v>2.6537</v>
       </c>
       <c r="G3" t="n">
-        <v>2.662</v>
+        <v>2.3764</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1771</v>
+        <v>3.5204</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7156</v>
+        <v>1.9766</v>
       </c>
       <c r="J3" t="n">
-        <v>2.662</v>
+        <v>2.3764</v>
       </c>
       <c r="K3" t="n">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="L3" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3776</v>
+        <v>4.353</v>
       </c>
       <c r="N3" t="n">
-        <v>168</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4">
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4912</v>
+        <v>4.4338</v>
       </c>
       <c r="C4" t="n">
-        <v>1.609</v>
+        <v>1.5884</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4203</v>
+        <v>1.414</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4912</v>
+        <v>4.4338</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6227</v>
+        <v>2.6805</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8685</v>
+        <v>1.7533</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7589</v>
+        <v>3.6212</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0298</v>
+        <v>2.0332</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8685</v>
+        <v>1.7533</v>
       </c>
       <c r="K4" t="n">
         <v>44</v>
@@ -621,7 +621,7 @@
         <v>124</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8983</v>
+        <v>3.7865</v>
       </c>
       <c r="N4" t="n">
         <v>168</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4235</v>
+        <v>4.3117</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5847</v>
+        <v>1.5447</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3895</v>
+        <v>1.3584</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4235</v>
+        <v>4.3117</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7811</v>
+        <v>3.6784</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6424</v>
+        <v>0.6333</v>
       </c>
       <c r="H5" t="n">
-        <v>7.5812</v>
+        <v>7.3676</v>
       </c>
       <c r="I5" t="n">
-        <v>4.0938</v>
+        <v>4.1367</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6424</v>
+        <v>0.6333</v>
       </c>
       <c r="K5" t="n">
         <v>144</v>
@@ -667,7 +667,7 @@
         <v>122</v>
       </c>
       <c r="M5" t="n">
-        <v>4.7362</v>
+        <v>4.77</v>
       </c>
       <c r="N5" t="n">
         <v>266</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1158</v>
+        <v>4.0463</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4745</v>
+        <v>1.4496</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2494</v>
+        <v>1.2375</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1158</v>
+        <v>4.0463</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4769</v>
+        <v>3.441</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6389</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>6.5775</v>
+        <v>6.4764</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5518</v>
+        <v>3.6363</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6389</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>144</v>
@@ -713,7 +713,7 @@
         <v>122</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1907</v>
+        <v>4.2416</v>
       </c>
       <c r="N6" t="n">
         <v>266</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9626</v>
+        <v>3.8818</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4196</v>
+        <v>1.3907</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1797</v>
+        <v>1.1626</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9626</v>
+        <v>3.8818</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0479</v>
+        <v>3.0271</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9147</v>
+        <v>0.8547</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1621</v>
+        <v>4.9223</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7875</v>
+        <v>2.7637</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9147</v>
+        <v>0.8547</v>
       </c>
       <c r="K7" t="n">
         <v>144</v>
@@ -759,7 +759,7 @@
         <v>122</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7022</v>
+        <v>3.6184</v>
       </c>
       <c r="N7" t="n">
         <v>266</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8797</v>
+        <v>3.7724</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3899</v>
+        <v>1.3515</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1419</v>
+        <v>1.1127</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8797</v>
+        <v>3.7724</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0954</v>
+        <v>3.0608</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7843</v>
+        <v>0.7116</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3188</v>
+        <v>5.0491</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8721</v>
+        <v>2.8349</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7843</v>
+        <v>0.7116</v>
       </c>
       <c r="K8" t="n">
         <v>166</v>
@@ -805,7 +805,7 @@
         <v>54</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6564</v>
+        <v>3.5465</v>
       </c>
       <c r="N8" t="n">
         <v>220</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5739</v>
+        <v>3.6765</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2804</v>
+        <v>1.3171</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0027</v>
+        <v>1.069</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5739</v>
+        <v>3.6765</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4576</v>
+        <v>2.532</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1163</v>
+        <v>1.1445</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2145</v>
+        <v>3.0636</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7358</v>
+        <v>1.7201</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1163</v>
+        <v>1.1445</v>
       </c>
       <c r="K9" t="n">
         <v>44</v>
@@ -851,7 +851,7 @@
         <v>124</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8521</v>
+        <v>2.8646</v>
       </c>
       <c r="N9" t="n">
         <v>168</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3444</v>
+        <v>3.3248</v>
       </c>
       <c r="C10" t="n">
-        <v>1.1981</v>
+        <v>1.1911</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8982</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3444</v>
+        <v>3.3248</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5264</v>
+        <v>2.6142</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.7106</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4413</v>
+        <v>3.372</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8583</v>
+        <v>1.8933</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.7106</v>
       </c>
       <c r="K10" t="n">
         <v>166</v>
@@ -897,7 +897,7 @@
         <v>54</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6763</v>
+        <v>2.6039</v>
       </c>
       <c r="N10" t="n">
         <v>220</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9254</v>
+        <v>2.6995</v>
       </c>
       <c r="C11" t="n">
-        <v>1.048</v>
+        <v>0.9671</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7075</v>
+        <v>0.624</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9254</v>
+        <v>2.6995</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8456</v>
+        <v>1.6776</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0798</v>
+        <v>1.0219</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8456</v>
+        <v>1.6776</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9966</v>
+        <v>0.9419</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0798</v>
+        <v>1.0219</v>
       </c>
       <c r="K11" t="n">
         <v>44</v>
@@ -943,7 +943,7 @@
         <v>124</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0764</v>
+        <v>1.9638</v>
       </c>
       <c r="N11" t="n">
         <v>168</v>
@@ -952,35 +952,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5979</v>
+        <v>2.6416</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9307</v>
+        <v>0.9464</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5584</v>
+        <v>0.5976</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5979</v>
+        <v>2.6416</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5607</v>
+        <v>2.4447</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0372</v>
+        <v>0.1969</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5545</v>
+        <v>2.7359</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9194</v>
+        <v>1.5361</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0372</v>
+        <v>0.1969</v>
       </c>
       <c r="K12" t="n">
         <v>166</v>
@@ -989,7 +989,7 @@
         <v>54</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9566</v>
+        <v>1.733</v>
       </c>
       <c r="N12" t="n">
         <v>220</v>
@@ -998,35 +998,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.55</v>
+        <v>2.6125</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9135</v>
+        <v>0.9359</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5366</v>
+        <v>0.5843</v>
       </c>
       <c r="E13" t="n">
-        <v>2.55</v>
+        <v>2.6125</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3164</v>
+        <v>2.6021</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2336</v>
+        <v>0.0104</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7484</v>
+        <v>3.3268</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4841</v>
+        <v>1.8679</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2336</v>
+        <v>0.0104</v>
       </c>
       <c r="K13" t="n">
         <v>166</v>
@@ -1035,7 +1035,7 @@
         <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7177</v>
+        <v>1.8783</v>
       </c>
       <c r="N13" t="n">
         <v>220</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3311</v>
+        <v>2.3889</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8351</v>
+        <v>0.8558</v>
       </c>
       <c r="D14" t="n">
-        <v>0.437</v>
+        <v>0.4825</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3311</v>
+        <v>2.3889</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3311</v>
+        <v>2.3908</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.0019</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3772</v>
+        <v>2.5335</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3772</v>
+        <v>1.4225</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.0019</v>
       </c>
       <c r="K14" t="n">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3772</v>
+        <v>1.4206</v>
       </c>
       <c r="N14" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3269</v>
+        <v>2.2869</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8336</v>
+        <v>0.8193</v>
       </c>
       <c r="D15" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3269</v>
+        <v>2.2869</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2963</v>
+        <v>2.2869</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0306</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6823</v>
+        <v>2.2906</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4484</v>
+        <v>2.2906</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0306</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="L15" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.479</v>
+        <v>2.2906</v>
       </c>
       <c r="N15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9854</v>
+        <v>1.9649</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7113</v>
+        <v>0.7039</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2796</v>
+        <v>0.2893</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9854</v>
+        <v>1.9649</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9854</v>
+        <v>2.9649</v>
       </c>
       <c r="G16" t="n">
         <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>4.9558</v>
+        <v>4.6888</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6761</v>
+        <v>2.6326</v>
       </c>
       <c r="J16" t="n">
         <v>-1</v>
@@ -1173,7 +1173,7 @@
         <v>54</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6761</v>
+        <v>1.6326</v>
       </c>
       <c r="N16" t="n">
         <v>220</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8832</v>
+        <v>1.894</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6747</v>
+        <v>0.6785</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2331</v>
+        <v>0.257</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8832</v>
+        <v>1.894</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8832</v>
+        <v>1.894</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8832</v>
+        <v>1.894</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8832</v>
+        <v>1.894</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8832</v>
+        <v>1.894</v>
       </c>
       <c r="N17" t="n">
         <v>111</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7548</v>
+        <v>1.8662</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6287</v>
+        <v>0.6686</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1746</v>
+        <v>0.2444</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7548</v>
+        <v>1.8662</v>
       </c>
       <c r="F18" t="n">
-        <v>2.317</v>
+        <v>2.4099</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5622</v>
+        <v>-0.5437</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7506</v>
+        <v>2.6053</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4853</v>
+        <v>1.4628</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5622</v>
+        <v>-0.5437</v>
       </c>
       <c r="K18" t="n">
         <v>66</v>
@@ -1265,7 +1265,7 @@
         <v>52</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9231</v>
+        <v>0.9191000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>118</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3769</v>
+        <v>1.3128</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4933</v>
+        <v>0.4703</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0026</v>
+        <v>-0.0077</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3769</v>
+        <v>1.3128</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5241</v>
+        <v>1.3662</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1472</v>
+        <v>-0.0534</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5241</v>
+        <v>1.3662</v>
       </c>
       <c r="I19" t="n">
-        <v>0.823</v>
+        <v>0.7671</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1472</v>
+        <v>-0.0534</v>
       </c>
       <c r="K19" t="n">
         <v>44</v>
@@ -1311,7 +1311,7 @@
         <v>124</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6758</v>
+        <v>0.7137</v>
       </c>
       <c r="N19" t="n">
         <v>168</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1879</v>
+        <v>1.1131</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4256</v>
+        <v>0.3988</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0834</v>
+        <v>-0.0987</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1879</v>
+        <v>1.1131</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1879</v>
+        <v>1.1131</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1879</v>
+        <v>1.1131</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1879</v>
+        <v>1.1131</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1879</v>
+        <v>1.1131</v>
       </c>
       <c r="N20" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0422</v>
+        <v>1.0233</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3734</v>
+        <v>0.3666</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1498</v>
+        <v>-0.1396</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0422</v>
+        <v>1.0233</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0422</v>
+        <v>1.0233</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0422</v>
+        <v>1.0233</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0422</v>
+        <v>1.0233</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0422</v>
+        <v>1.0233</v>
       </c>
       <c r="N21" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.748</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2985</v>
+        <v>0.268</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2449</v>
+        <v>-0.265</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.748</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6139</v>
+        <v>0.5619</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2193</v>
+        <v>0.1861</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6139</v>
+        <v>0.5619</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3315</v>
+        <v>0.3155</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2193</v>
+        <v>0.1861</v>
       </c>
       <c r="K22" t="n">
         <v>66</v>
@@ -1449,7 +1449,7 @@
         <v>52</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5508</v>
+        <v>0.5016</v>
       </c>
       <c r="N22" t="n">
         <v>118</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6596</v>
+        <v>0.6019</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2363</v>
+        <v>0.2156</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3239</v>
+        <v>-0.3316</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6596</v>
+        <v>0.6019</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6596</v>
+        <v>0.6019</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6596</v>
+        <v>0.6019</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6596</v>
+        <v>0.6019</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6596</v>
+        <v>0.6019</v>
       </c>
       <c r="N23" t="n">
         <v>111</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5745</v>
+        <v>0.5908</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2058</v>
+        <v>0.2117</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3627</v>
+        <v>-0.3367</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5745</v>
+        <v>0.5908</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5745</v>
+        <v>0.5908</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5745</v>
+        <v>0.5908</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5745</v>
+        <v>0.5908</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5745</v>
+        <v>0.5908</v>
       </c>
       <c r="N24" t="n">
         <v>111</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3644</v>
+        <v>0.3868</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1305</v>
+        <v>0.1386</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4583</v>
+        <v>-0.4296</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3644</v>
+        <v>0.3868</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8448</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4804</v>
+        <v>-0.4423</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8448</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4562</v>
+        <v>0.4655</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4804</v>
+        <v>-0.4423</v>
       </c>
       <c r="K25" t="n">
         <v>66</v>
@@ -1587,7 +1587,7 @@
         <v>52</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0242</v>
+        <v>0.0232</v>
       </c>
       <c r="N25" t="n">
         <v>118</v>
@@ -1596,32 +1596,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2778</v>
+        <v>0.2318</v>
       </c>
       <c r="C26" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4977</v>
+        <v>-0.5002</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2778</v>
+        <v>0.2318</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2778</v>
+        <v>0.2318</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2778</v>
+        <v>0.2318</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2778</v>
+        <v>0.2318</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2778</v>
+        <v>0.2318</v>
       </c>
       <c r="N26" t="n">
         <v>94</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2566</v>
+        <v>0.2094</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0919</v>
+        <v>0.075</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5074</v>
+        <v>-0.5104</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2566</v>
+        <v>0.2094</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2566</v>
+        <v>0.2094</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2566</v>
+        <v>0.2094</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2566</v>
+        <v>0.2094</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2566</v>
+        <v>0.2094</v>
       </c>
       <c r="N27" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.231</v>
+        <v>0.1683</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0828</v>
+        <v>0.0603</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.519</v>
+        <v>-0.5291</v>
       </c>
       <c r="E28" t="n">
-        <v>0.231</v>
+        <v>0.1683</v>
       </c>
       <c r="F28" t="n">
-        <v>0.231</v>
+        <v>0.1683</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.231</v>
+        <v>0.1683</v>
       </c>
       <c r="I28" t="n">
-        <v>0.231</v>
+        <v>0.1683</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.231</v>
+        <v>0.1683</v>
       </c>
       <c r="N28" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1314</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0471</v>
+        <v>0.0327</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5644</v>
+        <v>-0.5642</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1314</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1314</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1314</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1314</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1314</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>94</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.279</v>
+        <v>-0.2579</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1</v>
+        <v>-0.0924</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7512</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.279</v>
+        <v>-0.2579</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.279</v>
+        <v>-0.2579</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.279</v>
+        <v>-0.2579</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.279</v>
+        <v>-0.2579</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.279</v>
+        <v>-0.2579</v>
       </c>
       <c r="N30" t="n">
         <v>111</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3656</v>
+        <v>-0.3732</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.131</v>
+        <v>-0.1337</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7906</v>
+        <v>-0.7758</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3656</v>
+        <v>-0.3732</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2483</v>
+        <v>-0.2166</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1173</v>
+        <v>-0.1566</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2483</v>
+        <v>-0.2166</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1341</v>
+        <v>-0.1216</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.1173</v>
+        <v>-0.1566</v>
       </c>
       <c r="K31" t="n">
         <v>66</v>
@@ -1863,7 +1863,7 @@
         <v>52</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2514</v>
+        <v>-0.2782</v>
       </c>
       <c r="N31" t="n">
         <v>118</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3863</v>
+        <v>-0.4283</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1384</v>
+        <v>-0.1534</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8001</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3863</v>
+        <v>-0.4283</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3863</v>
+        <v>-0.4283</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3863</v>
+        <v>-0.4283</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3863</v>
+        <v>-0.4283</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3863</v>
+        <v>-0.4283</v>
       </c>
       <c r="N32" t="n">
         <v>94</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4247</v>
+        <v>-0.4432</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1521</v>
+        <v>-0.1588</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8175</v>
+        <v>-0.8077</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4247</v>
+        <v>-0.4432</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4247</v>
+        <v>-0.4432</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4247</v>
+        <v>-0.4432</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4247</v>
+        <v>-0.4432</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4247</v>
+        <v>-0.4432</v>
       </c>
       <c r="N33" t="n">
         <v>113</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4272</v>
+        <v>-0.4577</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.153</v>
+        <v>-0.164</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8187</v>
+        <v>-0.8143</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4272</v>
+        <v>-0.4577</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4272</v>
+        <v>-0.4577</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4272</v>
+        <v>-0.4577</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4272</v>
+        <v>-0.4577</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4272</v>
+        <v>-0.4577</v>
       </c>
       <c r="N34" t="n">
         <v>94</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6357</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.232</v>
+        <v>-0.2277</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.919</v>
+        <v>-0.8954</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6357</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6357</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6357</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6357</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6357</v>
       </c>
       <c r="N35" t="n">
         <v>94</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7821</v>
+        <v>-0.8079</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2802</v>
+        <v>-0.2894</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9802</v>
+        <v>-0.9738</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7821</v>
+        <v>-0.8079</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7821</v>
+        <v>-0.8079</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7821</v>
+        <v>-0.8079</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7821</v>
+        <v>-0.8079</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7821</v>
+        <v>-0.8079</v>
       </c>
       <c r="N36" t="n">
         <v>113</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8065</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2889</v>
+        <v>-0.2992</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9913</v>
+        <v>-0.9863</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8065</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8065</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8065</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8065</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8065</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="N37" t="n">
         <v>94</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8629</v>
+        <v>-0.8734</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3091</v>
+        <v>-0.3129</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.017</v>
+        <v>-1.0037</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8629</v>
+        <v>-0.8734</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8629</v>
+        <v>-0.8734</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8629</v>
+        <v>-0.8734</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8629</v>
+        <v>-0.8734</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8629</v>
+        <v>-0.8734</v>
       </c>
       <c r="N38" t="n">
         <v>94</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9911</v>
+        <v>-0.9484</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3551</v>
+        <v>-0.3398</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0754</v>
+        <v>-1.0378</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9911</v>
+        <v>-0.9484</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9911</v>
+        <v>-0.9484</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9911</v>
+        <v>-0.9484</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9911</v>
+        <v>-0.9484</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9911</v>
+        <v>-0.9484</v>
       </c>
       <c r="N39" t="n">
         <v>113</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.224</v>
+        <v>-1.1474</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4385</v>
+        <v>-0.4111</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1814</v>
+        <v>-1.1285</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.224</v>
+        <v>-1.1474</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.224</v>
+        <v>-1.1474</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.224</v>
+        <v>-1.1474</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.224</v>
+        <v>-1.1474</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.224</v>
+        <v>-1.1474</v>
       </c>
       <c r="N40" t="n">
         <v>94</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.193</v>
+        <v>-3.0825</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.1439</v>
+        <v>-1.1043</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0777</v>
+        <v>-2.01</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.193</v>
+        <v>-3.0825</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.3128</v>
+        <v>-2.2861</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.8802</v>
+        <v>-0.7964</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.3128</v>
+        <v>-2.2861</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.2489</v>
+        <v>-1.2836</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8802</v>
+        <v>-0.7964</v>
       </c>
       <c r="K41" t="n">
         <v>144</v>
@@ -2323,7 +2323,7 @@
         <v>122</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.1291</v>
+        <v>-2.08</v>
       </c>
       <c r="N41" t="n">
         <v>266</v>
@@ -2429,10 +2429,10 @@
         <v>1.14</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3466</v>
+        <v>0.2935</v>
       </c>
       <c r="J2" t="n">
-        <v>12.131</v>
+        <v>10.2725</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.92</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1179</v>
+        <v>-0.1012</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.1265</v>
+        <v>-3.542</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.89</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1517</v>
+        <v>-0.133</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.3095</v>
+        <v>-4.655</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.86</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1839</v>
+        <v>-0.1642</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.4365</v>
+        <v>-5.747</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.8</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2451</v>
+        <v>-0.2252</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.5785</v>
+        <v>-7.882</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.41</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9909</v>
+        <v>0.9818</v>
       </c>
       <c r="J7" t="n">
-        <v>34.6815</v>
+        <v>34.363</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.556</v>
+        <v>0.5182</v>
       </c>
       <c r="J8" t="n">
-        <v>19.46</v>
+        <v>18.137</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.17</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4885</v>
+        <v>0.4498</v>
       </c>
       <c r="J9" t="n">
-        <v>17.0975</v>
+        <v>15.743</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1916</v>
+        <v>-0.1569</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.706</v>
+        <v>-5.4915</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4185</v>
+        <v>-0.3761</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.6475</v>
+        <v>-13.1635</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.13</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3044</v>
+        <v>0.2539</v>
       </c>
       <c r="J12" t="n">
-        <v>10.654</v>
+        <v>8.8865</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2478</v>
+        <v>0.2023</v>
       </c>
       <c r="J13" t="n">
-        <v>8.673</v>
+        <v>7.0805</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.06</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1663</v>
+        <v>0.1304</v>
       </c>
       <c r="J14" t="n">
-        <v>5.8205</v>
+        <v>4.564</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.01</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0412</v>
+        <v>0.0284</v>
       </c>
       <c r="J15" t="n">
-        <v>1.442</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.84</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2144</v>
+        <v>-0.1938</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.504</v>
+        <v>-6.783</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.46</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1022</v>
+        <v>1.1071</v>
       </c>
       <c r="J17" t="n">
-        <v>38.577</v>
+        <v>38.7485</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.09</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3001</v>
+        <v>0.2633</v>
       </c>
       <c r="J18" t="n">
-        <v>10.5035</v>
+        <v>9.2155</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.99</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0725</v>
+        <v>-0.0527</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.5375</v>
+        <v>-1.8445</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.98</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1138</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.983</v>
+        <v>-3.059</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.9</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3586</v>
+        <v>-0.316</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.551</v>
+        <v>-11.06</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.31</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7033</v>
+        <v>0.6878</v>
       </c>
       <c r="J22" t="n">
-        <v>20.3957</v>
+        <v>19.9462</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4608</v>
+        <v>0.4294</v>
       </c>
       <c r="J23" t="n">
-        <v>13.3632</v>
+        <v>12.4526</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.16</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4608</v>
+        <v>0.4294</v>
       </c>
       <c r="J24" t="n">
-        <v>13.3632</v>
+        <v>12.4526</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.07</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2445</v>
+        <v>0.2115</v>
       </c>
       <c r="J25" t="n">
-        <v>7.0905</v>
+        <v>6.1335</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5847</v>
+        <v>-0.5465</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.9563</v>
+        <v>-15.8485</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.3</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5381</v>
+        <v>0.5097</v>
       </c>
       <c r="J27" t="n">
-        <v>15.6049</v>
+        <v>14.7813</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.2</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4136</v>
+        <v>0.3584</v>
       </c>
       <c r="J28" t="n">
-        <v>11.9944</v>
+        <v>10.3936</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.13</v>
       </c>
       <c r="I29" t="n">
-        <v>0.294</v>
+        <v>0.2464</v>
       </c>
       <c r="J29" t="n">
-        <v>8.526</v>
+        <v>7.1456</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.12</v>
       </c>
       <c r="I30" t="n">
-        <v>0.276</v>
+        <v>0.2301</v>
       </c>
       <c r="J30" t="n">
-        <v>8.004</v>
+        <v>6.6729</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3094</v>
+        <v>-0.2929</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.9726</v>
+        <v>-8.4941</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.52</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9698</v>
+        <v>0.9566</v>
       </c>
       <c r="J32" t="n">
-        <v>24.245</v>
+        <v>23.915</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.31</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6771</v>
+        <v>0.6663</v>
       </c>
       <c r="J33" t="n">
-        <v>16.9275</v>
+        <v>16.6575</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.27</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6191</v>
+        <v>0.6108</v>
       </c>
       <c r="J34" t="n">
-        <v>15.4775</v>
+        <v>15.27</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.15</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4216</v>
+        <v>0.3903</v>
       </c>
       <c r="J35" t="n">
-        <v>10.54</v>
+        <v>9.7575</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.11</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3244</v>
+        <v>0.2923</v>
       </c>
       <c r="J36" t="n">
-        <v>8.109999999999999</v>
+        <v>7.3075</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.16</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4044</v>
+        <v>0.3522</v>
       </c>
       <c r="J37" t="n">
-        <v>10.11</v>
+        <v>8.805</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.08</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2462</v>
+        <v>0.2019</v>
       </c>
       <c r="J38" t="n">
-        <v>6.155</v>
+        <v>5.0475</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.96</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0604</v>
+        <v>-0.0495</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.51</v>
+        <v>-1.2375</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.8</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2388</v>
+        <v>-0.2197</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.97</v>
+        <v>-5.4925</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.28</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6952</v>
+        <v>-0.7286</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.38</v>
+        <v>-18.215</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.14</v>
       </c>
       <c r="I42" t="n">
-        <v>0.369</v>
+        <v>0.318</v>
       </c>
       <c r="J42" t="n">
-        <v>8.856</v>
+        <v>7.632</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.93</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.0856</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.3904</v>
+        <v>-2.0544</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.82</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2186</v>
+        <v>-0.1998</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.2464</v>
+        <v>-4.7952</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.75</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2863</v>
+        <v>-0.2681</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.8712</v>
+        <v>-6.4344</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.61</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4145</v>
+        <v>-0.4044</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.948</v>
+        <v>-9.7056</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.77</v>
       </c>
       <c r="I47" t="n">
-        <v>1.315</v>
+        <v>1.3222</v>
       </c>
       <c r="J47" t="n">
-        <v>31.56</v>
+        <v>31.7328</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.31</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6863</v>
+        <v>0.6727</v>
       </c>
       <c r="J48" t="n">
-        <v>16.4712</v>
+        <v>16.1448</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.06</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>0.1719</v>
       </c>
       <c r="J49" t="n">
-        <v>4.8</v>
+        <v>4.1256</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0332</v>
+        <v>-0.0276</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.7968</v>
+        <v>-0.6624</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.85</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5069</v>
+        <v>-0.4676</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.1656</v>
+        <v>-11.2224</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3169</v>
+        <v>0.2662</v>
       </c>
       <c r="J52" t="n">
-        <v>8.873200000000001</v>
+        <v>7.4536</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.11</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2972</v>
+        <v>0.2478</v>
       </c>
       <c r="J53" t="n">
-        <v>8.3216</v>
+        <v>6.9384</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.89</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1497</v>
+        <v>-0.1319</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.1916</v>
+        <v>-3.6932</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.78</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2618</v>
+        <v>-0.2425</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.3304</v>
+        <v>-6.79</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4626</v>
+        <v>-0.4581</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.9528</v>
+        <v>-12.8268</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.38</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7935</v>
+        <v>0.7776</v>
       </c>
       <c r="J57" t="n">
-        <v>22.218</v>
+        <v>21.7728</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.23</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5674</v>
+        <v>0.5584</v>
       </c>
       <c r="J58" t="n">
-        <v>15.8872</v>
+        <v>15.6352</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.22</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5516</v>
+        <v>0.5432</v>
       </c>
       <c r="J59" t="n">
-        <v>15.4448</v>
+        <v>15.2096</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.09</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2884</v>
+        <v>0.2556</v>
       </c>
       <c r="J60" t="n">
-        <v>8.075200000000001</v>
+        <v>7.1568</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2628</v>
+        <v>-0.2242</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.3584</v>
+        <v>-6.2776</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.75</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2631</v>
+        <v>-0.2498</v>
       </c>
       <c r="J62" t="n">
-        <v>-5.262</v>
+        <v>-4.996</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3207</v>
+        <v>-0.3092</v>
       </c>
       <c r="J63" t="n">
-        <v>-6.414</v>
+        <v>-6.184</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.68</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3299</v>
+        <v>-0.3185</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.598</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.63</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3729</v>
+        <v>-0.3623</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.458</v>
+        <v>-7.246</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.48</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5044</v>
+        <v>-0.503</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.088</v>
+        <v>-10.06</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.63</v>
       </c>
       <c r="I67" t="n">
-        <v>1.2232</v>
+        <v>1.2432</v>
       </c>
       <c r="J67" t="n">
-        <v>24.464</v>
+        <v>24.864</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.53</v>
       </c>
       <c r="I68" t="n">
-        <v>1.0991</v>
+        <v>1.1175</v>
       </c>
       <c r="J68" t="n">
-        <v>21.982</v>
+        <v>22.35</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.49</v>
       </c>
       <c r="I69" t="n">
-        <v>1.0481</v>
+        <v>1.0628</v>
       </c>
       <c r="J69" t="n">
-        <v>20.962</v>
+        <v>21.256</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.48</v>
       </c>
       <c r="I70" t="n">
-        <v>1.0343</v>
+        <v>1.0474</v>
       </c>
       <c r="J70" t="n">
-        <v>20.686</v>
+        <v>20.948</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.47</v>
       </c>
       <c r="I71" t="n">
-        <v>1.0199</v>
+        <v>1.0313</v>
       </c>
       <c r="J71" t="n">
-        <v>20.398</v>
+        <v>20.626</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.48</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8447</v>
+        <v>0.7927</v>
       </c>
       <c r="J72" t="n">
-        <v>24.4963</v>
+        <v>22.9883</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7436</v>
+        <v>0.6868</v>
       </c>
       <c r="J73" t="n">
-        <v>21.5644</v>
+        <v>19.9172</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.96</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0785</v>
+        <v>-0.063</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.2765</v>
+        <v>-1.827</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.87</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1868</v>
+        <v>-0.1662</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.4172</v>
+        <v>-4.8198</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.66</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3902</v>
+        <v>-0.3799</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.3158</v>
+        <v>-11.0171</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.3</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7704</v>
+        <v>0.742</v>
       </c>
       <c r="J77" t="n">
-        <v>22.3416</v>
+        <v>21.518</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.2</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5564</v>
+        <v>0.5185</v>
       </c>
       <c r="J78" t="n">
-        <v>16.1356</v>
+        <v>15.0365</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.19</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5341</v>
+        <v>0.4958</v>
       </c>
       <c r="J79" t="n">
-        <v>15.4889</v>
+        <v>14.3782</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.07</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2415</v>
+        <v>0.2095</v>
       </c>
       <c r="J80" t="n">
-        <v>7.0035</v>
+        <v>6.0755</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.85</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4932</v>
+        <v>-0.4519</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.3028</v>
+        <v>-13.1051</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0419</v>
+        <v>0.0363</v>
       </c>
       <c r="J82" t="n">
-        <v>0.9637</v>
+        <v>0.8349</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.99</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0019</v>
+        <v>0.0045</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.0437</v>
+        <v>0.1035</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.85</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1844</v>
+        <v>-0.1679</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.2412</v>
+        <v>-3.8617</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.68</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3457</v>
+        <v>-0.3305</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.9511</v>
+        <v>-7.6015</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.47</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5312</v>
+        <v>-0.5346</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.2176</v>
+        <v>-12.2958</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.5</v>
       </c>
       <c r="I87" t="n">
-        <v>1.086</v>
+        <v>1.097</v>
       </c>
       <c r="J87" t="n">
-        <v>24.978</v>
+        <v>25.231</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.43</v>
       </c>
       <c r="I88" t="n">
-        <v>0.982</v>
+        <v>0.9784</v>
       </c>
       <c r="J88" t="n">
-        <v>22.586</v>
+        <v>22.5032</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.38</v>
       </c>
       <c r="I89" t="n">
-        <v>0.8924</v>
+        <v>0.8782</v>
       </c>
       <c r="J89" t="n">
-        <v>20.5252</v>
+        <v>20.1986</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.19</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5109</v>
+        <v>0.4803</v>
       </c>
       <c r="J90" t="n">
-        <v>11.7507</v>
+        <v>11.0469</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.98</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1512</v>
+        <v>-0.1253</v>
       </c>
       <c r="J91" t="n">
-        <v>-3.4776</v>
+        <v>-2.8819</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.92</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.0771</v>
+        <v>-0.0593</v>
       </c>
       <c r="J92" t="n">
-        <v>-1.6191</v>
+        <v>-1.2453</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.73</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2862</v>
+        <v>-0.2732</v>
       </c>
       <c r="J93" t="n">
-        <v>-6.0102</v>
+        <v>-5.7372</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.7</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3142</v>
+        <v>-0.3019</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.5982</v>
+        <v>-6.3399</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.6</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4014</v>
+        <v>-0.3913</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.429399999999999</v>
+        <v>-8.2173</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.38</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5945</v>
+        <v>-0.6058</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.4845</v>
+        <v>-12.7218</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>1.6774</v>
+        <v>1.7234</v>
       </c>
       <c r="J97" t="n">
-        <v>35.2254</v>
+        <v>36.1914</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.99</v>
       </c>
       <c r="I98" t="n">
-        <v>1.6657</v>
+        <v>1.7106</v>
       </c>
       <c r="J98" t="n">
-        <v>34.9797</v>
+        <v>35.9226</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.45</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9951</v>
+        <v>1.0004</v>
       </c>
       <c r="J99" t="n">
-        <v>20.8971</v>
+        <v>21.0084</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.19</v>
       </c>
       <c r="I100" t="n">
-        <v>0.487</v>
+        <v>0.4576</v>
       </c>
       <c r="J100" t="n">
-        <v>10.227</v>
+        <v>9.6096</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.65</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.9809</v>
+        <v>-0.9881</v>
       </c>
       <c r="J101" t="n">
-        <v>-20.5989</v>
+        <v>-20.7501</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.42</v>
       </c>
       <c r="I102" t="n">
-        <v>0.543</v>
+        <v>0.4733</v>
       </c>
       <c r="J102" t="n">
-        <v>14.661</v>
+        <v>12.7791</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.28</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3912</v>
+        <v>0.3299</v>
       </c>
       <c r="J103" t="n">
-        <v>10.5624</v>
+        <v>8.907299999999999</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.22</v>
       </c>
       <c r="I104" t="n">
-        <v>0.3226</v>
+        <v>0.2675</v>
       </c>
       <c r="J104" t="n">
-        <v>8.7102</v>
+        <v>7.2225</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.06</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1099</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="J105" t="n">
-        <v>2.9673</v>
+        <v>2.2437</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.0141</v>
+        <v>-0.0116</v>
       </c>
       <c r="J106" t="n">
-        <v>-0.3807</v>
+        <v>-0.3132</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.11</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2245</v>
+        <v>0.2084</v>
       </c>
       <c r="J107" t="n">
-        <v>6.0615</v>
+        <v>5.6268</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.08</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1769</v>
+        <v>0.1597</v>
       </c>
       <c r="J108" t="n">
-        <v>4.7763</v>
+        <v>4.3119</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.98</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0384</v>
+        <v>-0.03</v>
       </c>
       <c r="J109" t="n">
-        <v>-1.0368</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2945</v>
+        <v>-0.2762</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.9515</v>
+        <v>-7.4574</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.74</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.304</v>
+        <v>-0.2861</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.208</v>
+        <v>-7.7247</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.06</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2009</v>
+        <v>0.1608</v>
       </c>
       <c r="J112" t="n">
-        <v>4.6207</v>
+        <v>3.6984</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0881</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.0263</v>
+        <v>-1.7204</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.91</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1249</v>
+        <v>-0.1092</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.8727</v>
+        <v>-2.5116</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.71</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3248</v>
+        <v>-0.3081</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.4704</v>
+        <v>-7.0863</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.68</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3524</v>
+        <v>-0.3374</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.1052</v>
+        <v>-7.7602</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.45</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0159</v>
+        <v>1.0174</v>
       </c>
       <c r="J117" t="n">
-        <v>23.3657</v>
+        <v>23.4002</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.39</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8999</v>
       </c>
       <c r="J118" t="n">
-        <v>20.9944</v>
+        <v>20.6977</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.24</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6202</v>
+        <v>0.5921</v>
       </c>
       <c r="J119" t="n">
-        <v>14.2646</v>
+        <v>13.6183</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.21</v>
       </c>
       <c r="I120" t="n">
-        <v>0.5564</v>
+        <v>0.5265</v>
       </c>
       <c r="J120" t="n">
-        <v>12.7972</v>
+        <v>12.1095</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.14</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3966</v>
+        <v>0.3643</v>
       </c>
       <c r="J121" t="n">
-        <v>9.1218</v>
+        <v>8.3789</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.11</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2701</v>
+        <v>0.2221</v>
       </c>
       <c r="J122" t="n">
-        <v>11.3442</v>
+        <v>9.328200000000001</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.11</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2701</v>
+        <v>0.2221</v>
       </c>
       <c r="J123" t="n">
-        <v>11.3442</v>
+        <v>9.328200000000001</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.98</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0434</v>
+        <v>-0.0328</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.8228</v>
+        <v>-1.3776</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.96</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0733</v>
+        <v>-0.0587</v>
       </c>
       <c r="J125" t="n">
-        <v>-3.0786</v>
+        <v>-2.4654</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.89</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.1591</v>
+        <v>-0.139</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.6822</v>
+        <v>-5.838</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.52</v>
       </c>
       <c r="I127" t="n">
-        <v>1.1381</v>
+        <v>1.151</v>
       </c>
       <c r="J127" t="n">
-        <v>47.8002</v>
+        <v>48.342</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.4</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9556</v>
+        <v>0.9449</v>
       </c>
       <c r="J128" t="n">
-        <v>40.1352</v>
+        <v>39.6858</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.08</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2613</v>
+        <v>0.2297</v>
       </c>
       <c r="J129" t="n">
-        <v>10.9746</v>
+        <v>9.647399999999999</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.02</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0725</v>
+        <v>0.0562</v>
       </c>
       <c r="J130" t="n">
-        <v>3.045</v>
+        <v>2.3604</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.84</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5266</v>
+        <v>-0.4873</v>
       </c>
       <c r="J131" t="n">
-        <v>-22.1172</v>
+        <v>-20.4666</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.39</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9294</v>
+        <v>0.9156</v>
       </c>
       <c r="J132" t="n">
-        <v>21.3762</v>
+        <v>21.0588</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.34</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8101</v>
       </c>
       <c r="J133" t="n">
-        <v>19.1406</v>
+        <v>18.6323</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.26</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6705</v>
+        <v>0.6397</v>
       </c>
       <c r="J134" t="n">
-        <v>15.4215</v>
+        <v>14.7131</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.1</v>
       </c>
       <c r="I135" t="n">
-        <v>0.3096</v>
+        <v>0.2769</v>
       </c>
       <c r="J135" t="n">
-        <v>7.1208</v>
+        <v>6.3687</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.93</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2978</v>
+        <v>-0.2585</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.8494</v>
+        <v>-5.9455</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.04</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1546</v>
+        <v>0.1203</v>
       </c>
       <c r="J137" t="n">
-        <v>3.5558</v>
+        <v>2.7669</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.95</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0743</v>
+        <v>-0.0622</v>
       </c>
       <c r="J138" t="n">
-        <v>-1.7089</v>
+        <v>-1.4306</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.89</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1473</v>
+        <v>-0.1306</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.3879</v>
+        <v>-3.0038</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.73</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3057</v>
+        <v>-0.2882</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.0311</v>
+        <v>-6.6286</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.67</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3611</v>
+        <v>-0.3467</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.305300000000001</v>
+        <v>-7.9741</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.14</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2764</v>
+        <v>0.2638</v>
       </c>
       <c r="J142" t="n">
-        <v>7.1864</v>
+        <v>6.8588</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0117</v>
+        <v>0.0091</v>
       </c>
       <c r="J143" t="n">
-        <v>0.3042</v>
+        <v>0.2366</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.0781</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.3998</v>
+        <v>-2.0306</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.84</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2028</v>
+        <v>-0.1831</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.2728</v>
+        <v>-4.7606</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.58</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4459</v>
+        <v>-0.4395</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.5934</v>
+        <v>-11.427</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.42</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5465</v>
+        <v>0.4766</v>
       </c>
       <c r="J147" t="n">
-        <v>14.209</v>
+        <v>12.3916</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.16</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2525</v>
+        <v>0.2047</v>
       </c>
       <c r="J148" t="n">
-        <v>6.565</v>
+        <v>5.3222</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.13</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2139</v>
+        <v>0.1711</v>
       </c>
       <c r="J149" t="n">
-        <v>5.5614</v>
+        <v>4.4486</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.09</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1582</v>
+        <v>0.1234</v>
       </c>
       <c r="J150" t="n">
-        <v>4.1132</v>
+        <v>3.2084</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.06</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1122</v>
+        <v>0.0848</v>
       </c>
       <c r="J151" t="n">
-        <v>2.9172</v>
+        <v>2.2048</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.42</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9735</v>
+        <v>0.9671</v>
       </c>
       <c r="J152" t="n">
-        <v>25.311</v>
+        <v>25.1446</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.42</v>
       </c>
       <c r="I153" t="n">
-        <v>0.9735</v>
+        <v>0.9671</v>
       </c>
       <c r="J153" t="n">
-        <v>25.311</v>
+        <v>25.1446</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.39</v>
       </c>
       <c r="I154" t="n">
-        <v>0.9195</v>
+        <v>0.9059</v>
       </c>
       <c r="J154" t="n">
-        <v>23.907</v>
+        <v>23.5534</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.24</v>
       </c>
       <c r="I155" t="n">
-        <v>0.6243</v>
+        <v>0.5945</v>
       </c>
       <c r="J155" t="n">
-        <v>16.2318</v>
+        <v>15.457</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.78</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6788</v>
+        <v>-0.6499</v>
       </c>
       <c r="J156" t="n">
-        <v>-17.6488</v>
+        <v>-16.8974</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.02</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1202</v>
+        <v>0.0951</v>
       </c>
       <c r="J157" t="n">
-        <v>3.1252</v>
+        <v>2.4726</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.85</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1839</v>
+        <v>-0.1675</v>
       </c>
       <c r="J158" t="n">
-        <v>-4.7814</v>
+        <v>-4.355</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.84</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1944</v>
+        <v>-0.1778</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.0544</v>
+        <v>-4.6228</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.73</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2992</v>
+        <v>-0.2823</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.7792</v>
+        <v>-7.3398</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.53</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4789</v>
+        <v>-0.4753</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.4514</v>
+        <v>-12.3578</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.33</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6253</v>
+        <v>0.5656</v>
       </c>
       <c r="J162" t="n">
-        <v>25.6373</v>
+        <v>23.1896</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.32</v>
       </c>
       <c r="I163" t="n">
-        <v>0.61</v>
+        <v>0.5502</v>
       </c>
       <c r="J163" t="n">
-        <v>25.01</v>
+        <v>22.5582</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.03</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0931</v>
+        <v>0.0703</v>
       </c>
       <c r="J164" t="n">
-        <v>3.8171</v>
+        <v>2.8823</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.85</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2078</v>
+        <v>-0.1872</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.5198</v>
+        <v>-7.6752</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2285</v>
+        <v>-0.2083</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.368499999999999</v>
+        <v>-8.5403</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.08</v>
       </c>
       <c r="I167" t="n">
-        <v>0.2881</v>
+        <v>0.2481</v>
       </c>
       <c r="J167" t="n">
-        <v>11.8121</v>
+        <v>10.1721</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.07</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2599</v>
+        <v>0.2213</v>
       </c>
       <c r="J168" t="n">
-        <v>10.6559</v>
+        <v>9.0733</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.99</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0585</v>
+        <v>-0.0426</v>
       </c>
       <c r="J169" t="n">
-        <v>-2.3985</v>
+        <v>-1.7466</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.95</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1999</v>
+        <v>-0.1656</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.1959</v>
+        <v>-6.7896</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.9</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3416</v>
+        <v>-0.2997</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.0056</v>
+        <v>-12.2877</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.41</v>
       </c>
       <c r="I172" t="n">
-        <v>0.9585</v>
+        <v>0.9495</v>
       </c>
       <c r="J172" t="n">
-        <v>23.9625</v>
+        <v>23.7375</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.27</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6576</v>
       </c>
       <c r="J173" t="n">
-        <v>17.15</v>
+        <v>16.44</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.24</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6252</v>
+        <v>0.5948</v>
       </c>
       <c r="J174" t="n">
-        <v>15.63</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.16</v>
       </c>
       <c r="I175" t="n">
-        <v>0.4514</v>
+        <v>0.4182</v>
       </c>
       <c r="J175" t="n">
-        <v>11.285</v>
+        <v>10.455</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.11</v>
       </c>
       <c r="I176" t="n">
-        <v>0.3299</v>
+        <v>0.2974</v>
       </c>
       <c r="J176" t="n">
-        <v>8.2475</v>
+        <v>7.435</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.13</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3512</v>
+        <v>0.301</v>
       </c>
       <c r="J177" t="n">
-        <v>8.779999999999999</v>
+        <v>7.525</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.96</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0591</v>
+        <v>-0.0483</v>
       </c>
       <c r="J178" t="n">
-        <v>-1.4775</v>
+        <v>-1.2075</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.79</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2475</v>
+        <v>-0.2287</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.1875</v>
+        <v>-5.7175</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.74</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2953</v>
+        <v>-0.2774</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.3825</v>
+        <v>-6.935</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.61</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4141</v>
+        <v>-0.4039</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.3525</v>
+        <v>-10.0975</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.61</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2254</v>
+        <v>1.2415</v>
       </c>
       <c r="J182" t="n">
-        <v>30.635</v>
+        <v>31.0375</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.56</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1603</v>
+        <v>1.1744</v>
       </c>
       <c r="J183" t="n">
-        <v>29.0075</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.26</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6561</v>
+        <v>0.6311</v>
       </c>
       <c r="J184" t="n">
-        <v>16.4025</v>
+        <v>15.7775</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.14</v>
       </c>
       <c r="I185" t="n">
-        <v>0.39</v>
+        <v>0.3581</v>
       </c>
       <c r="J185" t="n">
-        <v>9.75</v>
+        <v>8.952500000000001</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.07</v>
       </c>
       <c r="I186" t="n">
-        <v>0.2075</v>
+        <v>0.1781</v>
       </c>
       <c r="J186" t="n">
-        <v>5.1875</v>
+        <v>4.4525</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.88</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1432</v>
+        <v>-0.1278</v>
       </c>
       <c r="J187" t="n">
-        <v>-3.58</v>
+        <v>-3.195</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.85</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1767</v>
+        <v>-0.1611</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.4175</v>
+        <v>-4.0275</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.73</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2942</v>
+        <v>-0.2787</v>
       </c>
       <c r="J189" t="n">
-        <v>-7.355</v>
+        <v>-6.9675</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.68</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3393</v>
+        <v>-0.3247</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.4825</v>
+        <v>-8.1175</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.57</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4377</v>
+        <v>-0.4295</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.9425</v>
+        <v>-10.7375</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.01</v>
       </c>
       <c r="I192" t="n">
-        <v>0.1739</v>
+        <v>0.1742</v>
       </c>
       <c r="J192" t="n">
-        <v>3.6519</v>
+        <v>3.6582</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.3166</v>
+        <v>-0.3056</v>
       </c>
       <c r="J193" t="n">
-        <v>-6.6486</v>
+        <v>-6.4176</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.62</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3791</v>
+        <v>-0.3698</v>
       </c>
       <c r="J194" t="n">
-        <v>-7.9611</v>
+        <v>-7.7658</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.52</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4655</v>
+        <v>-0.4604</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.775499999999999</v>
+        <v>-9.6684</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.26</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6938</v>
+        <v>-0.7231</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.5698</v>
+        <v>-15.1851</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>2.04</v>
       </c>
       <c r="I197" t="n">
-        <v>1.7093</v>
+        <v>1.7576</v>
       </c>
       <c r="J197" t="n">
-        <v>35.8953</v>
+        <v>36.9096</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.6</v>
       </c>
       <c r="I198" t="n">
-        <v>1.1856</v>
+        <v>1.2051</v>
       </c>
       <c r="J198" t="n">
-        <v>24.8976</v>
+        <v>25.3071</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.45</v>
       </c>
       <c r="I199" t="n">
-        <v>0.9889</v>
+        <v>0.9964</v>
       </c>
       <c r="J199" t="n">
-        <v>20.7669</v>
+        <v>20.9244</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.27</v>
       </c>
       <c r="I200" t="n">
-        <v>0.6489</v>
+        <v>0.6277</v>
       </c>
       <c r="J200" t="n">
-        <v>13.6269</v>
+        <v>13.1817</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.27</v>
       </c>
       <c r="I201" t="n">
-        <v>0.6489</v>
+        <v>0.6277</v>
       </c>
       <c r="J201" t="n">
-        <v>13.6269</v>
+        <v>13.1817</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.13</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3562</v>
+        <v>0.3068</v>
       </c>
       <c r="J202" t="n">
-        <v>8.904999999999999</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.92</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1097</v>
+        <v>-0.0953</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.7425</v>
+        <v>-2.3825</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.76</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2749</v>
+        <v>-0.2567</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.8725</v>
+        <v>-6.4175</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.75</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2844</v>
+        <v>-0.2664</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.11</v>
+        <v>-6.66</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.6</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4214</v>
+        <v>-0.4119</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.535</v>
+        <v>-10.2975</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.94</v>
       </c>
       <c r="I207" t="n">
-        <v>1.6492</v>
+        <v>1.6968</v>
       </c>
       <c r="J207" t="n">
-        <v>41.23</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.22</v>
       </c>
       <c r="I208" t="n">
-        <v>0.5782</v>
+        <v>0.5488</v>
       </c>
       <c r="J208" t="n">
-        <v>14.455</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.2</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5349</v>
+        <v>0.5044</v>
       </c>
       <c r="J209" t="n">
-        <v>13.3725</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.13</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3726</v>
+        <v>0.3403</v>
       </c>
       <c r="J210" t="n">
-        <v>9.315</v>
+        <v>8.5075</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.93</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3113</v>
+        <v>-0.2737</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.7825</v>
+        <v>-6.8425</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.65</v>
       </c>
       <c r="I212" t="n">
-        <v>1.2642</v>
+        <v>1.2826</v>
       </c>
       <c r="J212" t="n">
-        <v>24.0198</v>
+        <v>24.3694</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.53</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1106</v>
+        <v>1.1253</v>
       </c>
       <c r="J213" t="n">
-        <v>21.1014</v>
+        <v>21.3807</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.5</v>
       </c>
       <c r="I214" t="n">
-        <v>1.0713</v>
+        <v>1.0837</v>
       </c>
       <c r="J214" t="n">
-        <v>20.3547</v>
+        <v>20.5903</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.27</v>
       </c>
       <c r="I215" t="n">
-        <v>0.6667</v>
+        <v>0.6445</v>
       </c>
       <c r="J215" t="n">
-        <v>12.6673</v>
+        <v>12.2455</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.05</v>
       </c>
       <c r="I216" t="n">
-        <v>0.137</v>
+        <v>0.1095</v>
       </c>
       <c r="J216" t="n">
-        <v>2.603</v>
+        <v>2.0805</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.88</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.1284</v>
+        <v>-0.1113</v>
       </c>
       <c r="J217" t="n">
-        <v>-2.4396</v>
+        <v>-2.1147</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.84</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.1742</v>
+        <v>-0.1581</v>
       </c>
       <c r="J218" t="n">
-        <v>-3.3098</v>
+        <v>-3.0039</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.71</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3058</v>
+        <v>-0.2931</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.8102</v>
+        <v>-5.5689</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.57</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4287</v>
+        <v>-0.4201</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.145300000000001</v>
+        <v>-7.9819</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.36</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6125</v>
+        <v>-0.627</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.6375</v>
+        <v>-11.913</v>
       </c>
     </row>
   </sheetData>
